--- a/tame_output/ON/bt/strategyON_20240427.xlsx
+++ b/tame_output/ON/bt/strategyON_20240427.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.1%</t>
+          <t>-601.0%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.4%</t>
+          <t>-276.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-305.3%</t>
+          <t>-305.2%</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-219.1%</t>
+          <t>-219.0%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963412</v>
+        <v>3.782918957963413</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82854791119281</v>
+        <v>3.828547911192811</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82804935326204</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389902</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788087</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527519</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749177</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.83595441148149</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862979</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102774</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353065</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544774</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712286</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349958</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972332</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145931</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009942</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966251</v>
+        <v>3.845043810966253</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046988</v>
+        <v>3.79126997604699</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412095</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144508</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900687</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473593</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978362</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887696</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675894</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734154</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212291</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786038</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273184</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.482833331463359</v>
+        <v>3.482833331463361</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.395326487491203</v>
+        <v>-4.393925423285187</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9984079126142473</v>
+        <v>0.9989683382966539</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8130087713227969</v>
+        <v>-0.8116077071167807</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.269089669130798</v>
+        <v>2.269930307654408</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240427.xlsx
+++ b/tame_output/ON/bt/strategyON_20240427.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.8%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>136.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-700.3%</t>
+          <t>-711.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-58.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>410.6%</t>
+          <t>431.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.0%</t>
+          <t>-611.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-280.5%</t>
+          <t>-284.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-45.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-53.2%</t>
+          <t>-65.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.3%</t>
+          <t>-280.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-37.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-344.9%</t>
+          <t>-355.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-39.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.9%</t>
+          <t>-172.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-305.2%</t>
+          <t>-315.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-207.3%</t>
+          <t>-213.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-219.0%</t>
+          <t>-225.0%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.217330049284726</v>
+        <v>0.108403317668984</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.209145767513086</v>
+        <v>3.165575074866789</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.605635449818444</v>
+        <v>1.496708718202702</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.085951442004009</v>
+        <v>4.020595403034564</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.01980144256506905</v>
+        <v>-0.1287281741808111</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.149234255270709</v>
+        <v>3.105663562624413</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.605635449818444</v>
+        <v>1.496708718202702</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.120892526501551</v>
+        <v>4.055536487532105</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.01476385183748252</v>
+        <v>-0.1236905834532245</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.149826731747082</v>
+        <v>3.106256039100785</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.661279906084761</v>
+        <v>1.552353174469019</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.152856640446679</v>
+        <v>4.087500601477234</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1773899318021211</v>
+        <v>-0.2863166634178631</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.063522681384964</v>
+        <v>3.019951988738667</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.498653826120122</v>
+        <v>1.38972709450438</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.034027374091633</v>
+        <v>3.968671335122188</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2431573218515332</v>
+        <v>-0.3520840534672752</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.038233334495669</v>
+        <v>2.994662641849372</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.498653826120122</v>
+        <v>1.38972709450438</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.035044983222103</v>
+        <v>3.969688944252658</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.2566928056282428</v>
+        <v>-0.3656195372439848</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.023447172972741</v>
+        <v>2.979876480326444</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.498653826120122</v>
+        <v>1.38972709450438</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.025673015209859</v>
+        <v>3.960316976240414</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3384647060559944</v>
+        <v>-0.4473914376717364</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.980821138756879</v>
+        <v>2.937250446110582</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.525689399526259</v>
+        <v>1.416762667910517</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.031977085208779</v>
+        <v>3.966621046239334</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4056738139278721</v>
+        <v>-0.5146005455436141</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.95870281244183</v>
+        <v>2.915132119795533</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.525689399526259</v>
+        <v>1.416762667910517</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.036742402042481</v>
+        <v>3.971386363073036</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.613239598319484</v>
+        <v>-0.722166329935226</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.873501294804425</v>
+        <v>2.829930602158129</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.318123615134647</v>
+        <v>1.209196883518905</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.910027727526755</v>
+        <v>3.844671688557309</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.030993621866321</v>
+        <v>-1.139920353482063</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.704326576890754</v>
+        <v>2.660755884244457</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9003695915878102</v>
+        <v>0.7914428599720681</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.657302204903716</v>
+        <v>3.59194616593427</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.252615555424438</v>
+        <v>-1.361542287040181</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.615544020066428</v>
+        <v>2.571973327420132</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8628434579004411</v>
+        <v>0.7539167262846991</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.634652741290216</v>
+        <v>3.569296702320771</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.460619613777516</v>
+        <v>-1.569546345393258</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.537234541279123</v>
+        <v>2.493663848632826</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8628434579004411</v>
+        <v>0.7539167262846991</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.639544885844141</v>
+        <v>3.574188846874696</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.672032034665491</v>
+        <v>-1.780958766281233</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.447751029261921</v>
+        <v>2.404180336615624</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6514310370124661</v>
+        <v>0.542504305396724</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.507778889649344</v>
+        <v>3.442422850679899</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.011190412254013</v>
+        <v>-2.120117143869755</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.305171977532961</v>
+        <v>2.261601284886664</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.312272659423944</v>
+        <v>0.2033459278082019</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.29736816240268</v>
+        <v>3.232012123433235</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.339207633981492</v>
+        <v>-2.448134365597234</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.194303378580738</v>
+        <v>2.150732685934441</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.01574456230353516</v>
+        <v>-0.1246712939192772</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.120896119104961</v>
+        <v>3.055540080135516</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.83253250551667</v>
+        <v>-2.941459237132412</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.005072180375235</v>
+        <v>1.961501487728938</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1207306765431539</v>
+        <v>-0.229657408158896</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.066003200969758</v>
+        <v>3.000647162000313</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.324917533540767</v>
+        <v>-3.433844265156509</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.809224561209329</v>
+        <v>1.765653868563032</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.7220424361829927</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.771678576199033</v>
+        <v>2.706322537229587</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.71009792447084</v>
+        <v>-3.819024656086581</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.653694943650163</v>
+        <v>1.610124251003866</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.7220424361829927</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.770221115011896</v>
+        <v>2.70486507604245</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.053780697697502</v>
+        <v>-4.162707429313244</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.517990957814114</v>
+        <v>1.474420265167817</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7210217565944688</v>
+        <v>-0.8299484882102108</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.707246607250181</v>
+        <v>2.641890568280736</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.41143104793585</v>
+        <v>-4.520357779551592</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.371036876375032</v>
+        <v>1.327466183728736</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.187598838448559</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.48876245576343</v>
+        <v>2.423406416793985</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.720665150931901</v>
+        <v>-4.829591882547643</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.249116161876872</v>
+        <v>1.205545469230575</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.187598838448559</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.49053538246369</v>
+        <v>2.425179343494245</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.152470944081688</v>
+        <v>-5.26139767569743</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.062726732084361</v>
+        <v>1.019156039438065</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.215089603274084</v>
+        <v>-1.324016334889826</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.395017772066334</v>
+        <v>2.329661733096889</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.387164938214241</v>
+        <v>-5.496091669829982</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.957133909433431</v>
+        <v>0.9135632167871344</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.317680067660571</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.387104307405978</v>
+        <v>2.321748268436532</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.722827585444693</v>
+        <v>-5.831754317060435</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8214494421972152</v>
+        <v>0.7778787495509185</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.317680067660571</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.385684899061943</v>
+        <v>2.320328860092498</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.086453830345007</v>
+        <v>-6.195380561960748</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6824865044713313</v>
+        <v>0.6389158118250347</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.306974972911954</v>
+        <v>-1.415901704527696</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.333239477175909</v>
+        <v>2.267883438206463</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.451581212983753</v>
+        <v>-6.560507944599495</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5356900664216639</v>
+        <v>0.4921193737753673</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.603285757210967</v>
+        <v>-1.712212488826709</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.154707521602333</v>
+        <v>2.089351482632888</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.860169990164431</v>
+        <v>-6.969096721780174</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3710160995641516</v>
+        <v>0.327445406917855</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.120801266007387</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.908315799308685</v>
+        <v>1.84295976033924</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.273152474305525</v>
+        <v>-7.382079205921268</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2010085383791749</v>
+        <v>0.1574378457328778</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.120801266007387</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.903501231780145</v>
+        <v>1.8381451928107</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.689544348592523</v>
+        <v>-7.798471080208265</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.03244583927325317</v>
+        <v>-0.01112485337304392</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.120801266007387</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.901495282389023</v>
+        <v>1.836139243419578</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.066221359122366</v>
+        <v>-8.175148090738109</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1079662742700052</v>
+        <v>-0.1515369669163023</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.120801266007387</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.911753973057702</v>
+        <v>1.846397934088257</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.412096181107175</v>
+        <v>-8.521022912722918</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2502166379182338</v>
+        <v>-0.2937873305645309</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.120801266007387</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.907853538203397</v>
+        <v>1.842497499233952</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.574238451570269</v>
+        <v>-8.683165183186011</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3166686260484699</v>
+        <v>-0.360239318694767</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.120801266007387</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.906258458258398</v>
+        <v>1.840902419288953</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.870899793380467</v>
+        <v>-8.979826524996209</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.431554186843341</v>
+        <v>-0.4751248794896381</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.189544401741266</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.868791552747279</v>
+        <v>1.803435513777834</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.304248901490702</v>
+        <v>-9.413175633106444</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6089201346218385</v>
+        <v>-0.6524908272681351</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.189544401741266</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.864765248212876</v>
+        <v>1.79940920924343</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.687250290233333</v>
+        <v>-9.796177021849076</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7622227914404749</v>
+        <v>-0.805793484086772</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.189544401741266</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.864663146891292</v>
+        <v>1.799307107921846</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.844649170446454</v>
+        <v>-9.953575902062196</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8226108275542932</v>
+        <v>-0.8661815202005898</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.346943281954387</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.772795334734849</v>
+        <v>1.707439295765404</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.20417949295046</v>
+        <v>-10.3131062245662</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9610726532578431</v>
+        <v>-1.004643345904141</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.346943281954387</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.778145638032899</v>
+        <v>1.712789599063454</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.53057952161547</v>
+        <v>-10.63950625323121</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.083716644766672</v>
+        <v>-1.127287337412968</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.564416579003658</v>
+        <v>-2.6733433106194</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.590221640791069</v>
+        <v>1.524865601821624</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.74972848968967</v>
+        <v>-10.85865522130541</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.168334481374581</v>
+        <v>-1.211905174020878</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.892492278693598</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.461774010568319</v>
+        <v>1.396417971598874</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.74603756473326</v>
+        <v>-10.854964296349</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.166858111392017</v>
+        <v>-1.210428804038314</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.892492278693598</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.461774010568319</v>
+        <v>1.396417971598874</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.95029574006312</v>
+        <v>-11.05922247167886</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.24304818440532</v>
+        <v>-1.286618877051617</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.911204491691844</v>
+        <v>-3.020131223307587</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.390703840918569</v>
+        <v>1.325347801949123</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.1683335116943</v>
+        <v>-11.27726024331004</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.325780738573355</v>
+        <v>-1.369351431219652</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.085975259787743</v>
+        <v>-3.194901991403486</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.290323934545465</v>
+        <v>1.22496789557602</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.09486368002685</v>
+        <v>-11.20379041164259</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.281021104412955</v>
+        <v>-1.324591797059251</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.012505428120295</v>
+        <v>-3.121432159736037</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.349777535039355</v>
+        <v>1.28442149606991</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.26998809741339</v>
+        <v>-11.37891482902913</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.336515650620055</v>
+        <v>-1.380086343266352</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.296556577122581</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.259258105354946</v>
+        <v>1.1939020663855</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.50444019142788</v>
+        <v>-11.61336692304362</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.437515653127447</v>
+        <v>-1.481086345773744</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.296556577122581</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.25203894045335</v>
+        <v>1.186682901483904</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.79224403596512</v>
+        <v>-11.90117076758086</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.559309381716318</v>
+        <v>-1.602880074362615</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.475433690044077</v>
+        <v>-3.584360421659819</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.072684442957031</v>
+        <v>1.007328403987585</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.02206848312894</v>
+        <v>-12.13099521474469</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.650123370743292</v>
+        <v>-1.693694063389589</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.638081227114237</v>
+        <v>-3.74700795872998</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9762117105534909</v>
+        <v>0.9108556715840455</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.25409740286521</v>
+        <v>-12.36302413448095</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.740241210008682</v>
+        <v>-1.78381190265498</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.809020655918403</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9416978208695514</v>
+        <v>0.876341781900106</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.20208188889639</v>
+        <v>-12.31100862051214</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.715444668734756</v>
+        <v>-1.759015361381053</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.809020655918403</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9456881565559523</v>
+        <v>0.8803321175865069</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.34375373062051</v>
+        <v>-12.45268046223626</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.773588632323146</v>
+        <v>-1.817159324969443</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.809020655918403</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9442129296572106</v>
+        <v>0.8788568906877652</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.44266047107979</v>
+        <v>-12.55158720269553</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.798097918341984</v>
+        <v>-1.841668610988281</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.799000664761936</v>
+        <v>-3.907927396377679</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8999222955465176</v>
+        <v>0.8345662565770722</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.24350836384269</v>
+        <v>-12.35243509545843</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.731488209093828</v>
+        <v>-1.775058901740124</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.633678138812123</v>
+        <v>-3.742604870427865</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9860646774697228</v>
+        <v>0.920708638500277</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.01766321112328</v>
+        <v>-12.12658994273902</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.631571074969854</v>
+        <v>-1.675141767616151</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.700678194840702</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.02079975585823</v>
+        <v>0.9554437168887842</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.73138839880058</v>
+        <v>-11.84031513041633</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.515922005484717</v>
+        <v>-1.559492698131014</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.700678194840702</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.021938900414288</v>
+        <v>0.9565828614448431</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78428368684487</v>
+        <v>-11.89321041846061</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.534446346540324</v>
+        <v>-1.578017039186621</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.695722848752256</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.027545882229464</v>
+        <v>0.9621898432600182</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50037495591612</v>
+        <v>-11.60930168753186</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.415149149930188</v>
+        <v>-1.458719842576484</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.695722848752256</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.0332795864681</v>
+        <v>0.9679235474986547</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.38495403177802</v>
+        <v>-11.49388076339377</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.378718042668814</v>
+        <v>-1.422288735315112</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.58030192461416</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.092794878557092</v>
+        <v>1.027438839587647</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.12111716457395</v>
+        <v>-11.2300438961897</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.283066777100094</v>
+        <v>-1.326637469746391</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.58030192461416</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.082911397244185</v>
+        <v>1.017555358274739</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.85387536370556</v>
+        <v>-10.9628020953213</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.178004617252109</v>
+        <v>-1.221575309898406</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.58030192461416</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.081076836744811</v>
+        <v>1.015720797775366</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.73056943522734</v>
+        <v>-10.83949616684308</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.128982560834282</v>
+        <v>-1.172553253480579</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.381957521870854</v>
+        <v>-3.490884253486597</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.134427124447888</v>
+        <v>1.069071085478443</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.70661589425138</v>
+        <v>-10.81554262586712</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.118732638298405</v>
+        <v>-1.162303330944702</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.358003980894897</v>
+        <v>-3.466930712510639</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.149467755178956</v>
+        <v>1.084111716209511</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.44255595592858</v>
+        <v>-10.55148268754433</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.026368979131039</v>
+        <v>-1.069939671777336</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.202870774187843</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.294643402010882</v>
+        <v>1.229287363041436</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.735476332423746</v>
+        <v>-9.844403064039488</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7463241633894047</v>
+        <v>-0.7898948560357018</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.202870774187843</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.291856368350581</v>
+        <v>1.226500329381135</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.695292034057555</v>
+        <v>-9.804218765673298</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7299068201550871</v>
+        <v>-0.7734775128013842</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.05375974420591</v>
+        <v>-3.162686475821652</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.316310571258137</v>
+        <v>1.250954532288691</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.615222238519751</v>
+        <v>-9.724148970135493</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6985120807192082</v>
+        <v>-0.7420827733655053</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.973689948668106</v>
+        <v>-3.082616680283848</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.363719269801576</v>
+        <v>1.298363230832131</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.381741016290153</v>
+        <v>-9.490667747905896</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5971951629895171</v>
+        <v>-0.6407658556358138</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.740208726438507</v>
+        <v>-2.84913545805425</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.511732431977188</v>
+        <v>1.446376393007742</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.20203248614628</v>
+        <v>-9.310959217762022</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5282039612449267</v>
+        <v>-0.5717746538912238</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.683037222275811</v>
+        <v>-2.791963953891554</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.543143124161846</v>
+        <v>1.477787085192401</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.069757012515392</v>
+        <v>-9.178683744131135</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4799262850455448</v>
+        <v>-0.5234969776918419</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.550761748644925</v>
+        <v>-2.659688480260667</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.617875895087405</v>
+        <v>1.552519856117959</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.879157337842239</v>
+        <v>-8.988084069457981</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4008713544886469</v>
+        <v>-0.4444420471349435</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.469088805587515</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.735050760578933</v>
+        <v>1.669694721609488</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.630157539158658</v>
+        <v>-8.7390842707744</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2883650937915556</v>
+        <v>-0.3319357864378527</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.469088805587515</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.747957101802592</v>
+        <v>1.682601062833146</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.735747528931762</v>
+        <v>-8.844674260547505</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4585770193000158</v>
+        <v>-0.5021477119463129</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.574678795360619</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.556627178339511</v>
+        <v>1.491271139370065</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.754482431050359</v>
+        <v>-8.863409162666102</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4175266382703686</v>
+        <v>-0.4610973309166653</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.574678795360619</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.605171520216597</v>
+        <v>1.539815481247151</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.60654238964276</v>
+        <v>-8.715469121258502</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4782295443954965</v>
+        <v>-0.5218002370417931</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.445431147836319</v>
+        <v>-2.554357879452061</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.497485147073564</v>
+        <v>1.432129108104119</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.582313753253787</v>
+        <v>-8.69124048486953</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4772520760933854</v>
+        <v>-0.5208227687396825</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.530129243063089</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.503308342653469</v>
+        <v>1.437952303684024</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.538765346483096</v>
+        <v>-8.647692078098839</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4667933254802019</v>
+        <v>-0.510364018126499</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.530129243063089</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.496347730558376</v>
+        <v>1.43099169158893</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.296616953029238</v>
+        <v>-8.40554368464498</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3554716137175156</v>
+        <v>-0.3990423063638127</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.530129243063089</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.510810084939519</v>
+        <v>1.445454045970074</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.233387581260891</v>
+        <v>-8.342314312876633</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3356477445509816</v>
+        <v>-0.3792184371972787</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.530129243063089</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.505342205398714</v>
+        <v>1.439986166429269</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.046899888883884</v>
+        <v>-8.155826620499626</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2635545735896021</v>
+        <v>-0.3071252662358992</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.23471481907034</v>
+        <v>-2.343641550686083</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.614732914835495</v>
+        <v>1.549376875866049</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.025750689980441</v>
+        <v>-8.134677421596184</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2473939157908998</v>
+        <v>-0.2909646084371968</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.213565620166897</v>
+        <v>-2.322492351782639</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.635123412414886</v>
+        <v>1.56976737344544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.781985247996997</v>
+        <v>-7.890911979612739</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1541070306504717</v>
+        <v>-0.1976777232967684</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.213565620166897</v>
+        <v>-2.322492351782639</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.630904120761937</v>
+        <v>1.565548081792491</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.517957180803737</v>
+        <v>-7.62688391241948</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.04637148985315154</v>
+        <v>-0.08994218249944863</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.011700221350944</v>
+        <v>-2.120626952966686</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.754147673971525</v>
+        <v>1.688791635002079</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.268106786854663</v>
+        <v>-7.377033518470405</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.0463107427101801</v>
+        <v>0.002740050063883448</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.011700221350944</v>
+        <v>-2.120626952966686</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.746889748955227</v>
+        <v>1.681533709985781</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.964539297850684</v>
+        <v>-7.073466029466426</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1713368618324207</v>
+        <v>0.1277661691861236</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.011700221350944</v>
+        <v>-2.120626952966686</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.750488872475876</v>
+        <v>1.68513283350643</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.89105938899867</v>
+        <v>-6.999986120614412</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2140563314277797</v>
+        <v>0.1704856387814826</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.938220312498929</v>
+        <v>-2.047147044114672</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.807904323841638</v>
+        <v>1.742548284872192</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.666026389329847</v>
+        <v>-6.77495312094559</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3030900089116058</v>
+        <v>0.2595193162653091</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.713187312830106</v>
+        <v>-1.822114044445849</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.941944601259229</v>
+        <v>1.876588562289783</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.45139201169344</v>
+        <v>-6.560318743309183</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3936385610204858</v>
+        <v>0.3500678683741891</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.498552935193699</v>
+        <v>-1.607479666809442</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.07542002889539</v>
+        <v>2.010063989925944</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.184791654719088</v>
+        <v>-6.293718386334831</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4814729625940224</v>
+        <v>0.4379022699477253</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.498552935193699</v>
+        <v>-1.607479666809442</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.056614287679186</v>
+        <v>1.99125824870974</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.944361157914228</v>
+        <v>-6.053287889529971</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5793882379408437</v>
+        <v>0.5358175452945466</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.258122438388839</v>
+        <v>-1.367049170004582</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.202615662386979</v>
+        <v>2.137259623417534</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.701570350264783</v>
+        <v>-5.810497081880525</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6804338748354422</v>
+        <v>0.6368631821891451</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.258122438388839</v>
+        <v>-1.367049170004582</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.206544976221799</v>
+        <v>2.141188937252354</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.585630500639597</v>
+        <v>-5.69455723225534</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7274883986028562</v>
+        <v>0.6839177059565595</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.181300707372715</v>
+        <v>-1.290227438988458</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.253316598748814</v>
+        <v>2.187960559779368</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.342974912216434</v>
+        <v>-5.451901643832176</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8215487051921153</v>
+        <v>0.7779780125458182</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.181300707372715</v>
+        <v>-1.290227438988458</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.250314669968807</v>
+        <v>2.184958630999362</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.122954114179423</v>
+        <v>-5.231880845795166</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9111360614175337</v>
+        <v>0.8675653687712366</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.040080862304735</v>
+        <v>-1.149007593920478</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.33662561402021</v>
+        <v>2.271269575050764</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.923705484274614</v>
+        <v>-5.032632215890357</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.006729696181281</v>
+        <v>0.9631590035349835</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.040080862304735</v>
+        <v>-1.149007593920478</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.352519796822033</v>
+        <v>2.287163757852587</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.764190380755244</v>
+        <v>-4.873117112370987</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.07168158202933</v>
+        <v>1.028110889383033</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8805657587853651</v>
+        <v>-0.9894924904011076</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.449374703373957</v>
+        <v>2.384018664404511</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.619518235655507</v>
+        <v>-4.728444967271249</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.139638542630665</v>
+        <v>1.096067849984368</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7358936136856278</v>
+        <v>-0.8448203453013703</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.546266092995239</v>
+        <v>2.480910054025793</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.679393063013199</v>
+        <v>-4.788319794628942</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.101726103089014</v>
+        <v>1.058155410442717</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7957684410433199</v>
+        <v>-0.9046951726590624</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.49637868798205</v>
+        <v>2.431022649012604</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.592593565234191</v>
+        <v>-4.701520296849933</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.158846395523184</v>
+        <v>1.115275702876886</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7957684410433199</v>
+        <v>-0.9046951726590624</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.518779181304616</v>
+        <v>2.45342314233517</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.492900950505179</v>
+        <v>-4.601827682120922</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.1987958427882</v>
+        <v>1.155225150141904</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6960758263143081</v>
+        <v>-0.8050025579300506</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.578667151515435</v>
+        <v>2.513311112545989</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.561271136829189</v>
+        <v>-4.670197868444932</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.182454690733298</v>
+        <v>1.138883998087001</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6868001272780931</v>
+        <v>-0.7957268588938357</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.595239493411866</v>
+        <v>2.52988345444242</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.439854707202713</v>
+        <v>-4.548781438818455</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.22145797121578</v>
+        <v>1.177887278569483</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6868001272780931</v>
+        <v>-0.7957268588938357</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.585676202043757</v>
+        <v>2.520320163074312</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.470847866531418</v>
+        <v>-4.579774598147161</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.033770272524685</v>
+        <v>0.990199579878388</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6868001272780931</v>
+        <v>-0.7957268588938357</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.410385767084144</v>
+        <v>2.345029728114699</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.295373606738949</v>
+        <v>-4.404300338354691</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.108527208433461</v>
+        <v>1.064956515787164</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6868001272780931</v>
+        <v>-0.7957268588938357</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.414952999075932</v>
+        <v>2.349596960106486</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.406309859380197</v>
+        <v>-4.51523659099594</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.064164181263759</v>
+        <v>1.020593488617461</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6868001272780931</v>
+        <v>-0.7957268588938357</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.414964472962729</v>
+        <v>2.349608433993284</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.609336436923431</v>
+        <v>-4.718263168539173</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9860849354663708</v>
+        <v>0.9425142428200739</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8898267048213265</v>
+        <v>-0.998753436437069</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.296279911656695</v>
+        <v>2.230923872687249</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.451410837988138</v>
+        <v>-4.56033756960388</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.05942756147262</v>
+        <v>1.015856868826323</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8898267048213265</v>
+        <v>-0.998753436437069</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.306452298088827</v>
+        <v>2.241096259119382</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.599732091799266</v>
+        <v>-4.708658823415009</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9950453305220293</v>
+        <v>0.9514746378757322</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8898267048213265</v>
+        <v>-0.998753436437069</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.301398568662687</v>
+        <v>2.236042529693242</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.600915176450327</v>
+        <v>-4.709841908066069</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9863478721061305</v>
+        <v>0.9427771794598336</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8954697532878381</v>
+        <v>-1.004396484903581</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.289788515027306</v>
+        <v>2.22443247605786</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.477787469456244</v>
+        <v>-4.586714201071986</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.036150827936865</v>
+        <v>0.9925801352905683</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8954697532878381</v>
+        <v>-1.004396484903581</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.290340388060407</v>
+        <v>2.224984349090962</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.482833331463361</v>
+        <v>3.558916663178728</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.393925423285187</v>
+        <v>-4.493903719621127</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9989683382966539</v>
+        <v>0.9589770197622778</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8116077071167807</v>
+        <v>-0.9115860034527213</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.269930307654408</v>
+        <v>2.209943329852843</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240427.xlsx
+++ b/tame_output/ON/bt/strategyON_20240427.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>48.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.9%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-711.2%</t>
+          <t>-700.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-57.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>431.5%</t>
+          <t>414.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-611.0%</t>
+          <t>-593.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-284.9%</t>
+          <t>-280.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-65.7%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.3%</t>
+          <t>-273.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-355.8%</t>
+          <t>-344.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-172.9%</t>
+          <t>-167.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-315.2%</t>
+          <t>-304.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-213.8%</t>
+          <t>-207.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-225.0%</t>
+          <t>-218.5%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.108403317668984</v>
+        <v>0.217330049284726</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.165575074866789</v>
+        <v>3.209145767513086</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.496708718202702</v>
+        <v>1.605635449818444</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.020595403034564</v>
+        <v>4.085951442004009</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.1287281741808111</v>
+        <v>-0.01980144256506905</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.105663562624413</v>
+        <v>3.149234255270709</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.496708718202702</v>
+        <v>1.605635449818444</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.055536487532105</v>
+        <v>4.120892526501551</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.1236905834532245</v>
+        <v>-0.01476385183748252</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.106256039100785</v>
+        <v>3.149826731747082</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.552353174469019</v>
+        <v>1.661279906084761</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.087500601477234</v>
+        <v>4.152856640446679</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2863166634178631</v>
+        <v>-0.1773899318021211</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.019951988738667</v>
+        <v>3.063522681384964</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.38972709450438</v>
+        <v>1.498653826120122</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.968671335122188</v>
+        <v>4.034027374091633</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3520840534672752</v>
+        <v>-0.2431573218515332</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.994662641849372</v>
+        <v>3.038233334495669</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.38972709450438</v>
+        <v>1.498653826120122</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.969688944252658</v>
+        <v>4.035044983222103</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3656195372439848</v>
+        <v>-0.2566928056282428</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.979876480326444</v>
+        <v>3.023447172972741</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.38972709450438</v>
+        <v>1.498653826120122</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.960316976240414</v>
+        <v>4.025673015209859</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4473914376717364</v>
+        <v>-0.3384647060559944</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.937250446110582</v>
+        <v>2.980821138756879</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.416762667910517</v>
+        <v>1.525689399526259</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.966621046239334</v>
+        <v>4.031977085208779</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5146005455436141</v>
+        <v>-0.4056738139278721</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.915132119795533</v>
+        <v>2.95870281244183</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.416762667910517</v>
+        <v>1.525689399526259</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.971386363073036</v>
+        <v>4.036742402042481</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.722166329935226</v>
+        <v>-0.613239598319484</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.829930602158129</v>
+        <v>2.873501294804425</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.209196883518905</v>
+        <v>1.318123615134647</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.844671688557309</v>
+        <v>3.910027727526755</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.139920353482063</v>
+        <v>-1.030993621866321</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.660755884244457</v>
+        <v>2.704326576890754</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.7914428599720681</v>
+        <v>0.9003695915878102</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.59194616593427</v>
+        <v>3.657302204903716</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.361542287040181</v>
+        <v>-1.252615555424438</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.571973327420132</v>
+        <v>2.615544020066428</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.7539167262846991</v>
+        <v>0.8628434579004411</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.569296702320771</v>
+        <v>3.634652741290216</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.569546345393258</v>
+        <v>-1.460619613777516</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.493663848632826</v>
+        <v>2.537234541279123</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.7539167262846991</v>
+        <v>0.8628434579004411</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.574188846874696</v>
+        <v>3.639544885844141</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.780958766281233</v>
+        <v>-1.672032034665491</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.404180336615624</v>
+        <v>2.447751029261921</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.542504305396724</v>
+        <v>0.6514310370124661</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.442422850679899</v>
+        <v>3.507778889649344</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.120117143869755</v>
+        <v>-2.011190412254013</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.261601284886664</v>
+        <v>2.305171977532961</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2033459278082019</v>
+        <v>0.312272659423944</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.232012123433235</v>
+        <v>3.29736816240268</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.448134365597234</v>
+        <v>-2.339207633981492</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.150732685934441</v>
+        <v>2.194303378580738</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.1246712939192772</v>
+        <v>-0.01574456230353516</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.055540080135516</v>
+        <v>3.120896119104961</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.941459237132412</v>
+        <v>-2.83253250551667</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.961501487728938</v>
+        <v>2.005072180375235</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.229657408158896</v>
+        <v>-0.1207306765431539</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.000647162000313</v>
+        <v>3.066003200969758</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.433844265156509</v>
+        <v>-3.324917533540767</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.765653868563032</v>
+        <v>1.809224561209329</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.7220424361829927</v>
+        <v>-0.6131157045672506</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.706322537229587</v>
+        <v>2.771678576199033</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.819024656086581</v>
+        <v>-3.71009792447084</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.610124251003866</v>
+        <v>1.653694943650163</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.7220424361829927</v>
+        <v>-0.6131157045672506</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.70486507604245</v>
+        <v>2.770221115011896</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.162707429313244</v>
+        <v>-4.053780697697502</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.474420265167817</v>
+        <v>1.517990957814114</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.8299484882102108</v>
+        <v>-0.7210217565944688</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.641890568280736</v>
+        <v>2.707246607250181</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.520357779551592</v>
+        <v>-4.41143104793585</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.327466183728736</v>
+        <v>1.371036876375032</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.187598838448559</v>
+        <v>-1.078672106832817</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.423406416793985</v>
+        <v>2.48876245576343</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.829591882547643</v>
+        <v>-4.720665150931901</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.205545469230575</v>
+        <v>1.249116161876872</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.187598838448559</v>
+        <v>-1.078672106832817</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.425179343494245</v>
+        <v>2.49053538246369</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.26139767569743</v>
+        <v>-5.152470944081688</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.019156039438065</v>
+        <v>1.062726732084361</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.324016334889826</v>
+        <v>-1.215089603274084</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.329661733096889</v>
+        <v>2.395017772066334</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.496091669829982</v>
+        <v>-5.387164938214241</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9135632167871344</v>
+        <v>0.957133909433431</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.317680067660571</v>
+        <v>-1.208753336044829</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.321748268436532</v>
+        <v>2.387104307405978</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.831754317060435</v>
+        <v>-5.722827585444693</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7778787495509185</v>
+        <v>0.8214494421972152</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.317680067660571</v>
+        <v>-1.208753336044829</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.320328860092498</v>
+        <v>2.385684899061943</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.195380561960748</v>
+        <v>-6.086453830345007</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6389158118250347</v>
+        <v>0.6824865044713313</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.415901704527696</v>
+        <v>-1.306974972911954</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.267883438206463</v>
+        <v>2.333239477175909</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.560507944599495</v>
+        <v>-6.451581212983753</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.4921193737753673</v>
+        <v>0.5356900664216639</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.712212488826709</v>
+        <v>-1.603285757210967</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.089351482632888</v>
+        <v>2.154707521602333</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.969096721780174</v>
+        <v>-6.860169990164431</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.327445406917855</v>
+        <v>0.3710160995641516</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.120801266007387</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.84295976033924</v>
+        <v>1.908315799308685</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.382079205921268</v>
+        <v>-7.273152474305525</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1574378457328778</v>
+        <v>0.2010085383791749</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.120801266007387</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.8381451928107</v>
+        <v>1.903501231780145</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.798471080208265</v>
+        <v>-7.689544348592523</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.01112485337304392</v>
+        <v>0.03244583927325317</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.120801266007387</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.836139243419578</v>
+        <v>1.901495282389023</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.175148090738109</v>
+        <v>-8.066221359122366</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1515369669163023</v>
+        <v>-0.1079662742700052</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.120801266007387</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.846397934088257</v>
+        <v>1.911753973057702</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.521022912722918</v>
+        <v>-8.412096181107175</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2937873305645309</v>
+        <v>-0.2502166379182338</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.120801266007387</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.842497499233952</v>
+        <v>1.907853538203397</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.683165183186011</v>
+        <v>-8.574238451570269</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.360239318694767</v>
+        <v>-0.3166686260484699</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.120801266007387</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.840902419288953</v>
+        <v>1.906258458258398</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.979826524996209</v>
+        <v>-8.870899793380467</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4751248794896381</v>
+        <v>-0.431554186843341</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.189544401741266</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.803435513777834</v>
+        <v>1.868791552747279</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.413175633106444</v>
+        <v>-9.304248901490702</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6524908272681351</v>
+        <v>-0.6089201346218385</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.189544401741266</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.79940920924343</v>
+        <v>1.864765248212876</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.796177021849076</v>
+        <v>-9.687250290233333</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.805793484086772</v>
+        <v>-0.7622227914404749</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.189544401741266</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.799307107921846</v>
+        <v>1.864663146891292</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.953575902062196</v>
+        <v>-9.844649170446454</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8661815202005898</v>
+        <v>-0.8226108275542932</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.346943281954387</v>
+        <v>-2.238016550338645</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.707439295765404</v>
+        <v>1.772795334734849</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.3131062245662</v>
+        <v>-10.20417949295046</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.004643345904141</v>
+        <v>-0.9610726532578431</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.346943281954387</v>
+        <v>-2.238016550338645</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.712789599063454</v>
+        <v>1.778145638032899</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.63950625323121</v>
+        <v>-10.53057952161547</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.127287337412968</v>
+        <v>-1.083716644766672</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.6733433106194</v>
+        <v>-2.564416579003658</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.524865601821624</v>
+        <v>1.590221640791069</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.85865522130541</v>
+        <v>-10.74972848968967</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.211905174020878</v>
+        <v>-1.168334481374581</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.892492278693598</v>
+        <v>-2.783565547077855</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.396417971598874</v>
+        <v>1.461774010568319</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.854964296349</v>
+        <v>-10.74603756473326</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.210428804038314</v>
+        <v>-1.166858111392017</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.892492278693598</v>
+        <v>-2.783565547077855</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.396417971598874</v>
+        <v>1.461774010568319</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.05922247167886</v>
+        <v>-10.95029574006312</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.286618877051617</v>
+        <v>-1.24304818440532</v>
       </c>
       <c r="F1878" t="n">
-        <v>-3.020131223307587</v>
+        <v>-2.911204491691844</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.325347801949123</v>
+        <v>1.390703840918569</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.27726024331004</v>
+        <v>-11.1683335116943</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.369351431219652</v>
+        <v>-1.325780738573355</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.194901991403486</v>
+        <v>-3.085975259787743</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.22496789557602</v>
+        <v>1.290323934545465</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.20379041164259</v>
+        <v>-11.09486368002685</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.324591797059251</v>
+        <v>-1.281021104412955</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.121432159736037</v>
+        <v>-3.012505428120295</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.28442149606991</v>
+        <v>1.349777535039355</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.37891482902913</v>
+        <v>-11.26998809741339</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.380086343266352</v>
+        <v>-1.336515650620055</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.296556577122581</v>
+        <v>-3.187629845506839</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.1939020663855</v>
+        <v>1.259258105354946</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.61336692304362</v>
+        <v>-11.50444019142788</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.481086345773744</v>
+        <v>-1.437515653127447</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.296556577122581</v>
+        <v>-3.187629845506839</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.186682901483904</v>
+        <v>1.25203894045335</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.90117076758086</v>
+        <v>-11.79224403596512</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.602880074362615</v>
+        <v>-1.559309381716318</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.584360421659819</v>
+        <v>-3.475433690044077</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.007328403987585</v>
+        <v>1.072684442957031</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.13099521474469</v>
+        <v>-12.02206848312894</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.693694063389589</v>
+        <v>-1.650123370743292</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.74700795872998</v>
+        <v>-3.638081227114237</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9108556715840455</v>
+        <v>0.9762117105534909</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.36302413448095</v>
+        <v>-12.25409740286521</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.78381190265498</v>
+        <v>-1.740241210008682</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.809020655918403</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.876341781900106</v>
+        <v>0.9416978208695514</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.31100862051214</v>
+        <v>-12.20208188889639</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.759015361381053</v>
+        <v>-1.715444668734756</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.809020655918403</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.8803321175865069</v>
+        <v>0.9456881565559523</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.45268046223626</v>
+        <v>-12.34375373062051</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.817159324969443</v>
+        <v>-1.773588632323146</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.809020655918403</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.8788568906877652</v>
+        <v>0.9442129296572106</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.55158720269553</v>
+        <v>-12.44266047107979</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.841668610988281</v>
+        <v>-1.798097918341984</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.907927396377679</v>
+        <v>-3.799000664761936</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8345662565770722</v>
+        <v>0.8999222955465176</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.35243509545843</v>
+        <v>-12.24350836384269</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.775058901740124</v>
+        <v>-1.731488209093828</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.742604870427865</v>
+        <v>-3.633678138812123</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.920708638500277</v>
+        <v>0.9860646774697228</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.12658994273902</v>
+        <v>-12.01766321112328</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.675141767616151</v>
+        <v>-1.631571074969854</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.700678194840702</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9554437168887842</v>
+        <v>1.02079975585823</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.84031513041633</v>
+        <v>-11.73138839880058</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.559492698131014</v>
+        <v>-1.515922005484717</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.700678194840702</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9565828614448431</v>
+        <v>1.021938900414288</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.89321041846061</v>
+        <v>-11.78428368684487</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.578017039186621</v>
+        <v>-1.534446346540324</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.695722848752256</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9621898432600182</v>
+        <v>1.027545882229464</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.60930168753186</v>
+        <v>-11.50037495591612</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.458719842576484</v>
+        <v>-1.415149149930188</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.695722848752256</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9679235474986547</v>
+        <v>1.0332795864681</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.49388076339377</v>
+        <v>-11.38495403177802</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.422288735315112</v>
+        <v>-1.378718042668814</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.58030192461416</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.027438839587647</v>
+        <v>1.092794878557092</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.2300438961897</v>
+        <v>-11.12111716457395</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.326637469746391</v>
+        <v>-1.283066777100094</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.58030192461416</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.017555358274739</v>
+        <v>1.082911397244185</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.9628020953213</v>
+        <v>-10.85387536370556</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.221575309898406</v>
+        <v>-1.178004617252109</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.58030192461416</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.015720797775366</v>
+        <v>1.081076836744811</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.83949616684308</v>
+        <v>-10.73056943522734</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.172553253480579</v>
+        <v>-1.128982560834282</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.490884253486597</v>
+        <v>-3.381957521870854</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.069071085478443</v>
+        <v>1.134427124447888</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.81554262586712</v>
+        <v>-10.70661589425138</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.162303330944702</v>
+        <v>-1.118732638298405</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.466930712510639</v>
+        <v>-3.358003980894897</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.084111716209511</v>
+        <v>1.149467755178956</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.55148268754433</v>
+        <v>-10.44255595592858</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.069939671777336</v>
+        <v>-1.026368979131039</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.202870774187843</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.229287363041436</v>
+        <v>1.294643402010882</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.844403064039488</v>
+        <v>-9.735476332423746</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7898948560357018</v>
+        <v>-0.7463241633894047</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.202870774187843</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.226500329381135</v>
+        <v>1.291856368350581</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.804218765673298</v>
+        <v>-9.695292034057555</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7734775128013842</v>
+        <v>-0.7299068201550871</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.162686475821652</v>
+        <v>-3.05375974420591</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.250954532288691</v>
+        <v>1.316310571258137</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.724148970135493</v>
+        <v>-9.615222238519751</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7420827733655053</v>
+        <v>-0.6985120807192082</v>
       </c>
       <c r="F1902" t="n">
-        <v>-3.082616680283848</v>
+        <v>-2.973689948668106</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.298363230832131</v>
+        <v>1.363719269801576</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.490667747905896</v>
+        <v>-9.381741016290153</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6407658556358138</v>
+        <v>-0.5971951629895171</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.84913545805425</v>
+        <v>-2.740208726438507</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.446376393007742</v>
+        <v>1.511732431977188</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.310959217762022</v>
+        <v>-9.20203248614628</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5717746538912238</v>
+        <v>-0.5282039612449267</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.791963953891554</v>
+        <v>-2.683037222275811</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.477787085192401</v>
+        <v>1.543143124161846</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.178683744131135</v>
+        <v>-9.069757012515392</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5234969776918419</v>
+        <v>-0.4799262850455448</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.659688480260667</v>
+        <v>-2.550761748644925</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.552519856117959</v>
+        <v>1.617875895087405</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.988084069457981</v>
+        <v>-8.879157337842239</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4444420471349435</v>
+        <v>-0.4008713544886469</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.469088805587515</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.669694721609488</v>
+        <v>1.735050760578933</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.7390842707744</v>
+        <v>-8.630157539158658</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3319357864378527</v>
+        <v>-0.2883650937915556</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.469088805587515</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.682601062833146</v>
+        <v>1.747957101802592</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.844674260547505</v>
+        <v>-8.735747528931762</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5021477119463129</v>
+        <v>-0.4585770193000158</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.574678795360619</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.491271139370065</v>
+        <v>1.556627178339511</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.863409162666102</v>
+        <v>-8.754482431050359</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4610973309166653</v>
+        <v>-0.4175266382703686</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.574678795360619</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.539815481247151</v>
+        <v>1.605171520216597</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.715469121258502</v>
+        <v>-8.60654238964276</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5218002370417931</v>
+        <v>-0.4782295443954965</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.554357879452061</v>
+        <v>-2.445431147836319</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.432129108104119</v>
+        <v>1.497485147073564</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.69124048486953</v>
+        <v>-8.582313753253787</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5208227687396825</v>
+        <v>-0.4772520760933854</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.530129243063089</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.437952303684024</v>
+        <v>1.503308342653469</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.647692078098839</v>
+        <v>-8.538765346483096</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.510364018126499</v>
+        <v>-0.4667933254802019</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.530129243063089</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.43099169158893</v>
+        <v>1.496347730558376</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.40554368464498</v>
+        <v>-8.296616953029238</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3990423063638127</v>
+        <v>-0.3554716137175156</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.530129243063089</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.445454045970074</v>
+        <v>1.510810084939519</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.342314312876633</v>
+        <v>-8.162555244751095</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3792184371972787</v>
+        <v>-0.3073148099470635</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.530129243063089</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.439986166429269</v>
+        <v>1.505342205398714</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.155826620499626</v>
+        <v>-7.976067552374089</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3071252662358992</v>
+        <v>-0.2352216389856845</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.343641550686083</v>
+        <v>-2.23471481907034</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.549376875866049</v>
+        <v>1.614732914835495</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.134677421596184</v>
+        <v>-7.954918353470646</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2909646084371968</v>
+        <v>-0.2190609811869817</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.322492351782639</v>
+        <v>-2.213565620166897</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.56976737344544</v>
+        <v>1.635123412414886</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.890911979612739</v>
+        <v>-7.711152911487202</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1976777232967684</v>
+        <v>-0.1257740960465532</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.322492351782639</v>
+        <v>-2.213565620166897</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.565548081792491</v>
+        <v>1.630904120761937</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.62688391241948</v>
+        <v>-7.447124844293942</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.08994218249944863</v>
+        <v>-0.01803855524923348</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.120626952966686</v>
+        <v>-2.011700221350944</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.688791635002079</v>
+        <v>1.754147673971525</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.377033518470405</v>
+        <v>-7.197274450344867</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.002740050063883448</v>
+        <v>0.0746436773140986</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.120626952966686</v>
+        <v>-2.011700221350944</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.681533709985781</v>
+        <v>1.746889748955227</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.073466029466426</v>
+        <v>-6.893706961340889</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1277661691861236</v>
+        <v>0.1996697964363388</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.120626952966686</v>
+        <v>-2.011700221350944</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.68513283350643</v>
+        <v>1.750488872475876</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.999986120614412</v>
+        <v>-6.820227052488875</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1704856387814826</v>
+        <v>0.2423892660316977</v>
       </c>
       <c r="F1921" t="n">
-        <v>-2.047147044114672</v>
+        <v>-1.938220312498929</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.742548284872192</v>
+        <v>1.807904323841638</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.77495312094559</v>
+        <v>-6.595194052820052</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2595193162653091</v>
+        <v>0.3314229435155243</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.822114044445849</v>
+        <v>-1.713187312830106</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.876588562289783</v>
+        <v>1.941944601259229</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.560318743309183</v>
+        <v>-6.380559675183645</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3500678683741891</v>
+        <v>0.4219714956244043</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.607479666809442</v>
+        <v>-1.498552935193699</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.010063989925944</v>
+        <v>2.07542002889539</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.293718386334831</v>
+        <v>-6.113959318209293</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4379022699477253</v>
+        <v>0.5098058971979404</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.607479666809442</v>
+        <v>-1.498552935193699</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.99125824870974</v>
+        <v>2.056614287679186</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.053287889529971</v>
+        <v>-5.873528821404433</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5358175452945466</v>
+        <v>0.6077211725447622</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.367049170004582</v>
+        <v>-1.258122438388839</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.137259623417534</v>
+        <v>2.202615662386979</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.810497081880525</v>
+        <v>-5.630738013754987</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6368631821891451</v>
+        <v>0.7087668094393602</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.367049170004582</v>
+        <v>-1.258122438388839</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.141188937252354</v>
+        <v>2.206544976221799</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.69455723225534</v>
+        <v>-5.514798164129802</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6839177059565595</v>
+        <v>0.7558213332067747</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.290227438988458</v>
+        <v>-1.181300707372715</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.187960559779368</v>
+        <v>2.253316598748814</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.451901643832176</v>
+        <v>-5.272142575706638</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7779780125458182</v>
+        <v>0.8498816397960334</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.290227438988458</v>
+        <v>-1.181300707372715</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.184958630999362</v>
+        <v>2.250314669968807</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.231880845795166</v>
+        <v>-5.052121777669628</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8675653687712366</v>
+        <v>0.9394689960214517</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.149007593920478</v>
+        <v>-1.040080862304735</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.271269575050764</v>
+        <v>2.33662561402021</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.032632215890357</v>
+        <v>-4.852873147764819</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9631590035349835</v>
+        <v>1.035062630785199</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.149007593920478</v>
+        <v>-1.040080862304735</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.287163757852587</v>
+        <v>2.352519796822033</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.873117112370987</v>
+        <v>-4.693358044245449</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.028110889383033</v>
+        <v>1.100014516633248</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9894924904011076</v>
+        <v>-0.8805657587853651</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.384018664404511</v>
+        <v>2.449374703373957</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.728444967271249</v>
+        <v>-4.548685899145712</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.096067849984368</v>
+        <v>1.167971477234583</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.8448203453013703</v>
+        <v>-0.7358936136856278</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.480910054025793</v>
+        <v>2.546266092995239</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.788319794628942</v>
+        <v>-4.608560726503404</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.058155410442717</v>
+        <v>1.130059037692932</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.9046951726590624</v>
+        <v>-0.7957684410433199</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.431022649012604</v>
+        <v>2.49637868798205</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.701520296849933</v>
+        <v>-4.521761228724396</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.115275702876886</v>
+        <v>1.187179330127102</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.9046951726590624</v>
+        <v>-0.7957684410433199</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.45342314233517</v>
+        <v>2.518779181304616</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.601827682120922</v>
+        <v>-4.422068613995384</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.155225150141904</v>
+        <v>1.227128777392119</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.8050025579300506</v>
+        <v>-0.6960758263143081</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.513311112545989</v>
+        <v>2.578667151515435</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.670197868444932</v>
+        <v>-4.490438800319394</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.138883998087001</v>
+        <v>1.210787625337217</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7957268588938357</v>
+        <v>-0.6868001272780931</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.52988345444242</v>
+        <v>2.595239493411866</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.548781438818455</v>
+        <v>-4.369022370692917</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.177887278569483</v>
+        <v>1.249790905819698</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7957268588938357</v>
+        <v>-0.6868001272780931</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.520320163074312</v>
+        <v>2.585676202043757</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.579774598147161</v>
+        <v>-4.400015530021623</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.990199579878388</v>
+        <v>1.062103207128603</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7957268588938357</v>
+        <v>-0.6868001272780931</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.345029728114699</v>
+        <v>2.410385767084144</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.404300338354691</v>
+        <v>-4.224541270229153</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.064956515787164</v>
+        <v>1.136860143037379</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7957268588938357</v>
+        <v>-0.6868001272780931</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.349596960106486</v>
+        <v>2.414952999075932</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.51523659099594</v>
+        <v>-4.335477522870402</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.020593488617461</v>
+        <v>1.092497115867677</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7957268588938357</v>
+        <v>-0.6868001272780931</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.349608433993284</v>
+        <v>2.414964472962729</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.718263168539173</v>
+        <v>-4.538504100413635</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9425142428200739</v>
+        <v>1.014417870070289</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.998753436437069</v>
+        <v>-0.8898267048213265</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.230923872687249</v>
+        <v>2.296279911656695</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.56033756960388</v>
+        <v>-4.380578501478342</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.015856868826323</v>
+        <v>1.087760496076539</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.998753436437069</v>
+        <v>-0.8898267048213265</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.241096259119382</v>
+        <v>2.306452298088827</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.708658823415009</v>
+        <v>-4.528899755289471</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9514746378757322</v>
+        <v>1.023378265125947</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.998753436437069</v>
+        <v>-0.8898267048213265</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.236042529693242</v>
+        <v>2.301398568662687</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.709841908066069</v>
+        <v>-4.530082839940532</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9427771794598336</v>
+        <v>1.014680806710049</v>
       </c>
       <c r="F1944" t="n">
-        <v>-1.004396484903581</v>
+        <v>-0.8954697532878381</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.22443247605786</v>
+        <v>2.289788515027306</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.586714201071986</v>
+        <v>-4.406955132946448</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9925801352905683</v>
+        <v>1.064483762540783</v>
       </c>
       <c r="F1945" t="n">
-        <v>-1.004396484903581</v>
+        <v>-0.8954697532878381</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.224984349090962</v>
+        <v>2.290340388060407</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.558916663178728</v>
+        <v>3.767847990234354</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.493903719621127</v>
+        <v>-4.314144651495589</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9589770197622778</v>
+        <v>1.030880647012493</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.9115860034527213</v>
+        <v>-0.8026592718369787</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.209943329852843</v>
+        <v>2.275299368822289</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240427.xlsx
+++ b/tame_output/ON/bt/strategyON_20240427.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-26.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>136.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-218.5%</t>
+          <t>-161.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1946"/>
+  <dimension ref="A1:G1947"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153011</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575949</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430983</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457897</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879198</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568102</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963413</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192811</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.79126997604699</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734158</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212294</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202392378604</v>
+        <v>3.752023923786042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273185</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.767847990234354</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
@@ -46319,6 +46319,29 @@
       </c>
       <c r="G1946" t="n">
         <v>2.275299368822289</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="2" t="n">
+        <v>45409</v>
+      </c>
+      <c r="B1947" t="n">
+        <v>3.76855775544024</v>
+      </c>
+      <c r="C1947" t="n">
+        <v>2.852084684560143</v>
+      </c>
+      <c r="D1947" t="n">
+        <v>-4.314144651495589</v>
+      </c>
+      <c r="E1947" t="n">
+        <v>1.030880647012493</v>
+      </c>
+      <c r="F1947" t="n">
+        <v>-0.8026592718369787</v>
+      </c>
+      <c r="G1947" t="n">
+        <v>2.845148481546511</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240427.xlsx
+++ b/tame_output/ON/bt/strategyON_20240427.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>53.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-22.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.5%</t>
+          <t>135.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-700.3%</t>
+          <t>-685.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-57.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>414.0%</t>
+          <t>334.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.0%</t>
+          <t>-585.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-280.5%</t>
+          <t>-274.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-44.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-273.1%</t>
+          <t>-270.2%</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.9%</t>
+          <t>-168.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-161.5%</t>
+          <t>-157.9%</t>
         </is>
       </c>
     </row>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.01980144256506905</v>
+        <v>0.1245452526383835</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.149234255270709</v>
+        <v>3.206972933352091</v>
       </c>
       <c r="F1839" t="n">
         <v>1.605635449818444</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.01476385183748252</v>
+        <v>0.12958284336597</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.149826731747082</v>
+        <v>3.207565409828463</v>
       </c>
       <c r="F1840" t="n">
         <v>1.661279906084761</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1773899318021211</v>
+        <v>-0.03304323659866859</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.063522681384964</v>
+        <v>3.121261359466345</v>
       </c>
       <c r="F1841" t="n">
         <v>1.498653826120122</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2431573218515332</v>
+        <v>-0.09881062664808066</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.038233334495669</v>
+        <v>3.09597201257705</v>
       </c>
       <c r="F1842" t="n">
         <v>1.498653826120122</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.2566928056282428</v>
+        <v>-0.1123461104247903</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.023447172972741</v>
+        <v>3.081185851054122</v>
       </c>
       <c r="F1843" t="n">
         <v>1.498653826120122</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3384647060559944</v>
+        <v>-0.1941180108525419</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.980821138756879</v>
+        <v>3.038559816838259</v>
       </c>
       <c r="F1844" t="n">
         <v>1.525689399526259</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4056738139278721</v>
+        <v>-0.2613271187244196</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.95870281244183</v>
+        <v>3.016441490523211</v>
       </c>
       <c r="F1845" t="n">
         <v>1.525689399526259</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.613239598319484</v>
+        <v>-0.4688929031160315</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.873501294804425</v>
+        <v>2.931239972885806</v>
       </c>
       <c r="F1846" t="n">
         <v>1.318123615134647</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.030993621866321</v>
+        <v>-0.8866469266628685</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.704326576890754</v>
+        <v>2.762065254972135</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9003695915878102</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.252615555424438</v>
+        <v>-1.108268860220986</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.615544020066428</v>
+        <v>2.673282698147809</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8628434579004411</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.460619613777516</v>
+        <v>-1.316272918574063</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.537234541279123</v>
+        <v>2.594973219360504</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8628434579004411</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.672032034665491</v>
+        <v>-1.527685339462038</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.447751029261921</v>
+        <v>2.505489707343302</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6514310370124661</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.011190412254013</v>
+        <v>-1.866843717050561</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.305171977532961</v>
+        <v>2.362910655614342</v>
       </c>
       <c r="F1851" t="n">
         <v>0.312272659423944</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.339207633981492</v>
+        <v>-2.19486093877804</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.194303378580738</v>
+        <v>2.252042056662119</v>
       </c>
       <c r="F1852" t="n">
         <v>-0.01574456230353516</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.83253250551667</v>
+        <v>-2.688185810313218</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.005072180375235</v>
+        <v>2.062810858456616</v>
       </c>
       <c r="F1853" t="n">
         <v>-0.1207306765431539</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.324917533540767</v>
+        <v>-3.180570838337315</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.809224561209329</v>
+        <v>1.866963239290709</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.6131157045672506</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.71009792447084</v>
+        <v>-3.565751229267387</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.653694943650163</v>
+        <v>1.711433621731544</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.6131157045672506</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.053780697697502</v>
+        <v>-3.90943400249405</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.517990957814114</v>
+        <v>1.575729635895495</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.7210217565944688</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.41143104793585</v>
+        <v>-4.267084352732399</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.371036876375032</v>
+        <v>1.428775554456413</v>
       </c>
       <c r="F1857" t="n">
         <v>-1.078672106832817</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.720665150931901</v>
+        <v>-4.576318455728449</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.249116161876872</v>
+        <v>1.306854839958252</v>
       </c>
       <c r="F1858" t="n">
         <v>-1.078672106832817</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.152470944081688</v>
+        <v>-5.008124248878237</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.062726732084361</v>
+        <v>1.120465410165742</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.215089603274084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.387164938214241</v>
+        <v>-5.242818243010789</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.957133909433431</v>
+        <v>1.014872587514811</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.208753336044829</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.722827585444693</v>
+        <v>-5.578480890241241</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8214494421972152</v>
+        <v>0.8791881202785956</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.208753336044829</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.086453830345007</v>
+        <v>-5.942107135141555</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6824865044713313</v>
+        <v>0.7402251825527122</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.306974972911954</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.451581212983753</v>
+        <v>-6.307234517780302</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5356900664216639</v>
+        <v>0.5934287445030448</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.603285757210967</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.860169990164431</v>
+        <v>-6.71582329496098</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3710160995641516</v>
+        <v>0.428754777645532</v>
       </c>
       <c r="F1864" t="n">
         <v>-2.011874534391645</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.273152474305525</v>
+        <v>-7.128805779102074</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2010085383791749</v>
+        <v>0.2587472164605553</v>
       </c>
       <c r="F1865" t="n">
         <v>-2.011874534391645</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.689544348592523</v>
+        <v>-7.545197653389072</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.03244583927325317</v>
+        <v>0.09018451735463362</v>
       </c>
       <c r="F1866" t="n">
         <v>-2.011874534391645</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.066221359122366</v>
+        <v>-7.921874663918916</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1079662742700052</v>
+        <v>-0.05022759618862516</v>
       </c>
       <c r="F1867" t="n">
         <v>-2.011874534391645</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.412096181107175</v>
+        <v>-8.267749485903725</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2502166379182338</v>
+        <v>-0.1924779598368533</v>
       </c>
       <c r="F1868" t="n">
         <v>-2.011874534391645</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.574238451570269</v>
+        <v>-8.429891756366818</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3166686260484699</v>
+        <v>-0.2589299479670895</v>
       </c>
       <c r="F1869" t="n">
         <v>-2.011874534391645</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.870899793380467</v>
+        <v>-8.726553098177016</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.431554186843341</v>
+        <v>-0.3738155087619606</v>
       </c>
       <c r="F1870" t="n">
         <v>-2.080617670125524</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.304248901490702</v>
+        <v>-9.159902206287251</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6089201346218385</v>
+        <v>-0.551181456540458</v>
       </c>
       <c r="F1871" t="n">
         <v>-2.080617670125524</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.687250290233333</v>
+        <v>-9.542903595029882</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7622227914404749</v>
+        <v>-0.7044841133590944</v>
       </c>
       <c r="F1872" t="n">
         <v>-2.080617670125524</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.844649170446454</v>
+        <v>-9.700302475243003</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8226108275542932</v>
+        <v>-0.7648721494729127</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.238016550338645</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.20417949295046</v>
+        <v>-10.059832797747</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9610726532578431</v>
+        <v>-0.9033339751764631</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.238016550338645</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.53057952161547</v>
+        <v>-10.38623282641202</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.083716644766672</v>
+        <v>-1.025977966685291</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.564416579003658</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.74972848968967</v>
+        <v>-10.60538179448621</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.168334481374581</v>
+        <v>-1.110595803293201</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.783565547077855</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.74603756473326</v>
+        <v>-10.6016908695298</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.166858111392017</v>
+        <v>-1.109119433310636</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.783565547077855</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.95029574006312</v>
+        <v>-10.80594904485967</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.24304818440532</v>
+        <v>-1.185309506323939</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.911204491691844</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.1683335116943</v>
+        <v>-11.02398681649085</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.325780738573355</v>
+        <v>-1.268042060491975</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.085975259787743</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.09486368002685</v>
+        <v>-10.9505169848234</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.281021104412955</v>
+        <v>-1.223282426331574</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.012505428120295</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.26998809741339</v>
+        <v>-11.12564140220994</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.336515650620055</v>
+        <v>-1.278776972538674</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.187629845506839</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.50444019142788</v>
+        <v>-11.36009349622443</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.437515653127447</v>
+        <v>-1.379776975046066</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.187629845506839</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.79224403596512</v>
+        <v>-11.64789734076167</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.559309381716318</v>
+        <v>-1.501570703634938</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.475433690044077</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.02206848312894</v>
+        <v>-11.87772178792549</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.650123370743292</v>
+        <v>-1.592384692661912</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.638081227114237</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.25409740286521</v>
+        <v>-12.10975070766175</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.740241210008682</v>
+        <v>-1.682502531927302</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.70009392430266</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.20208188889639</v>
+        <v>-12.05773519369294</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.715444668734756</v>
+        <v>-1.657705990653376</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.70009392430266</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.34375373062051</v>
+        <v>-12.19940703541706</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.773588632323146</v>
+        <v>-1.715849954241766</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.70009392430266</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.44266047107979</v>
+        <v>-12.29831377587634</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.798097918341984</v>
+        <v>-1.740359240260604</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.799000664761936</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.24350836384269</v>
+        <v>-12.09916166863924</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.731488209093828</v>
+        <v>-1.673749531012447</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.633678138812123</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.01766321112328</v>
+        <v>-11.87331651591983</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.631571074969854</v>
+        <v>-1.573832396888474</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.591751463224959</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.73138839880058</v>
+        <v>-11.58704170359713</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.515922005484717</v>
+        <v>-1.458183327403337</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.591751463224959</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78428368684487</v>
+        <v>-11.63993699164142</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.534446346540324</v>
+        <v>-1.476707668458944</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.586796117136513</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50037495591612</v>
+        <v>-11.35602826071267</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.415149149930188</v>
+        <v>-1.357410471848808</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.586796117136513</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.38495403177802</v>
+        <v>-11.24060733657458</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.378718042668814</v>
+        <v>-1.320979364587435</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.471375192998417</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.12111716457395</v>
+        <v>-10.97677046937051</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.283066777100094</v>
+        <v>-1.225328099018715</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.471375192998417</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.85387536370556</v>
+        <v>-10.70952866850211</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.178004617252109</v>
+        <v>-1.120265939170729</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.471375192998417</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.73056943522734</v>
+        <v>-10.58622274002389</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.128982560834282</v>
+        <v>-1.071243882752902</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.381957521870854</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.70661589425138</v>
+        <v>-10.56226919904793</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.118732638298405</v>
+        <v>-1.060993960217025</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.358003980894897</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.44255595592858</v>
+        <v>-10.29820926072513</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.026368979131039</v>
+        <v>-0.9686303010496591</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.093944042572101</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.735476332423746</v>
+        <v>-9.591129637220297</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7463241633894047</v>
+        <v>-0.6885854853080251</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.093944042572101</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.695292034057555</v>
+        <v>-9.550945338854106</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7299068201550871</v>
+        <v>-0.6721681420737076</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.05375974420591</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.615222238519751</v>
+        <v>-9.470875543316302</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6985120807192082</v>
+        <v>-0.6407734026378287</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.973689948668106</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.381741016290153</v>
+        <v>-9.237394321086704</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5971951629895171</v>
+        <v>-0.5394564849081371</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.740208726438507</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.20203248614628</v>
+        <v>-9.057685790942831</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5282039612449267</v>
+        <v>-0.4704652831635472</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.683037222275811</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.069757012515392</v>
+        <v>-8.925410317311943</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4799262850455448</v>
+        <v>-0.4221876069641652</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.550761748644925</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.879157337842239</v>
+        <v>-8.73481064263879</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4008713544886469</v>
+        <v>-0.3431326764072669</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.360162073971772</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.630157539158658</v>
+        <v>-8.485810843955209</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2883650937915556</v>
+        <v>-0.2306264157101761</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.360162073971772</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.735747528931762</v>
+        <v>-8.591400833728313</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4585770193000158</v>
+        <v>-0.4008383412186363</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.465752063744877</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.754482431050359</v>
+        <v>-8.61013573584691</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4175266382703686</v>
+        <v>-0.3597879601889886</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.465752063744877</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.60654238964276</v>
+        <v>-8.462195694439311</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4782295443954965</v>
+        <v>-0.4204908663141165</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.445431147836319</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.582313753253787</v>
+        <v>-8.437967058050338</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4772520760933854</v>
+        <v>-0.4195133980120058</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.421202511447347</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.538765346483096</v>
+        <v>-8.394418651279647</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4667933254802019</v>
+        <v>-0.4090546473988224</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.421202511447347</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.296616953029238</v>
+        <v>-8.152270257825789</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3554716137175156</v>
+        <v>-0.297732935636136</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.421202511447347</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.162555244751095</v>
+        <v>-8.089040886057441</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3073148099470635</v>
+        <v>-0.277909066469602</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.421202511447347</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.976067552374089</v>
+        <v>-7.902553193680435</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2352216389856845</v>
+        <v>-0.205815895508223</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.23471481907034</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.954918353470646</v>
+        <v>-7.881403994776992</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2190609811869817</v>
+        <v>-0.1896552377095202</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.213565620166897</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.711152911487202</v>
+        <v>-7.637638552793548</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1257740960465532</v>
+        <v>-0.09636835256909171</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.213565620166897</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.447124844293942</v>
+        <v>-7.373610485600288</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.01803855524923348</v>
+        <v>0.01136718822822802</v>
       </c>
       <c r="F1918" t="n">
         <v>-2.011700221350944</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.197274450344867</v>
+        <v>-7.123760091651214</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.0746436773140986</v>
+        <v>0.1040494207915601</v>
       </c>
       <c r="F1919" t="n">
         <v>-2.011700221350944</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.893706961340889</v>
+        <v>-6.820192602647235</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1996697964363388</v>
+        <v>0.2290755399138003</v>
       </c>
       <c r="F1920" t="n">
         <v>-2.011700221350944</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.820227052488875</v>
+        <v>-6.746712693795221</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2423892660316977</v>
+        <v>0.2717950095091592</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.938220312498929</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.595194052820052</v>
+        <v>-6.521679694126398</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3314229435155243</v>
+        <v>0.3608286869929858</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.713187312830106</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.380559675183645</v>
+        <v>-6.307045316489991</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4219714956244043</v>
+        <v>0.4513772391018658</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.498552935193699</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.113959318209293</v>
+        <v>-6.040444959515639</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5098058971979404</v>
+        <v>0.5392116406754019</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.498552935193699</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.873528821404433</v>
+        <v>-5.800014462710779</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6077211725447622</v>
+        <v>0.6371269160222237</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.258122438388839</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.630738013754987</v>
+        <v>-5.557223655061334</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7087668094393602</v>
+        <v>0.7381725529168217</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.258122438388839</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.514798164129802</v>
+        <v>-5.441283805436148</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7558213332067747</v>
+        <v>0.7852270766842362</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.181300707372715</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.272142575706638</v>
+        <v>-5.198628217012985</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8498816397960334</v>
+        <v>0.8792873832734949</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.181300707372715</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.052121777669628</v>
+        <v>-4.978607418975974</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9394689960214517</v>
+        <v>0.9688747394989132</v>
       </c>
       <c r="F1929" t="n">
         <v>-1.040080862304735</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.852873147764819</v>
+        <v>-4.779358789071165</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.035062630785199</v>
+        <v>1.06446837426266</v>
       </c>
       <c r="F1930" t="n">
         <v>-1.040080862304735</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.693358044245449</v>
+        <v>-4.619843685551795</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.100014516633248</v>
+        <v>1.12942026011071</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.8805657587853651</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.548685899145712</v>
+        <v>-4.475171540452058</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.167971477234583</v>
+        <v>1.197377220712045</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.7358936136856278</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.608560726503404</v>
+        <v>-4.53504636780975</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.130059037692932</v>
+        <v>1.159464781170394</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.7957684410433199</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.521761228724396</v>
+        <v>-4.448246870030742</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.187179330127102</v>
+        <v>1.216585073604563</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.7957684410433199</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.422068613995384</v>
+        <v>-4.34855425530173</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.227128777392119</v>
+        <v>1.25653452086958</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.6960758263143081</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.490438800319394</v>
+        <v>-4.41692444162574</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.210787625337217</v>
+        <v>1.240193368814678</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.6868001272780931</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.369022370692917</v>
+        <v>-4.295508011999264</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.249790905819698</v>
+        <v>1.27919664929716</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.6868001272780931</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.400015530021623</v>
+        <v>-4.326501171327969</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.062103207128603</v>
+        <v>1.091508950606065</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.6868001272780931</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.224541270229153</v>
+        <v>-4.151026911535499</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.136860143037379</v>
+        <v>1.16626588651484</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.6868001272780931</v>
@@ -46171,10 +46171,10 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.335477522870402</v>
+        <v>-4.261963164176748</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.092497115867677</v>
+        <v>1.121902859345138</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.6868001272780931</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.538504100413635</v>
+        <v>-4.464989741719982</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.014417870070289</v>
+        <v>1.043823613547751</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.8898267048213265</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.380578501478342</v>
+        <v>-4.307064142784689</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.087760496076539</v>
+        <v>1.117166239554</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.8898267048213265</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.528899755289471</v>
+        <v>-4.455385396595817</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.023378265125947</v>
+        <v>1.052784008603409</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.8898267048213265</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.530082839940532</v>
+        <v>-4.456568481246878</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.014680806710049</v>
+        <v>1.04408655018751</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.8954697532878381</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.406955132946448</v>
+        <v>-4.333440774252795</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.064483762540783</v>
+        <v>1.093889506018245</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.8954697532878381</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.314144651495589</v>
+        <v>-4.240630292801935</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.030880647012493</v>
+        <v>1.060286390489954</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.8026592718369787</v>
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.76855775544024</v>
+        <v>3.81080229429443</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.852084684560143</v>
+        <v>2.888255231107191</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.314144651495589</v>
+        <v>-4.240630292801935</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.030880647012493</v>
+        <v>1.060286390489954</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.8026592718369787</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.845148481546511</v>
+        <v>2.881319028093559</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240427.xlsx
+++ b/tame_output/ON/bt/strategyON_20240427.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-46.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.4%</t>
+          <t>116.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.8%</t>
+          <t>135.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-685.9%</t>
+          <t>-687.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.2%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>334.8%</t>
+          <t>353.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-585.6%</t>
+          <t>-593.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-274.7%</t>
+          <t>-275.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.7%</t>
+          <t>-44.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-44.1%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-270.2%</t>
+          <t>-273.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-36.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-168.6%</t>
+          <t>-168.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-304.3%</t>
+          <t>-309.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.9%</t>
+          <t>-181.2%</t>
         </is>
       </c>
     </row>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1245452526383835</v>
+        <v>0.1036293896815316</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.206972933352091</v>
+        <v>3.19860658816935</v>
       </c>
       <c r="F1839" t="n">
         <v>1.605635449818444</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.12958284336597</v>
+        <v>0.1086669804091182</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.207565409828463</v>
+        <v>3.199199064645722</v>
       </c>
       <c r="F1840" t="n">
         <v>1.661279906084761</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.03304323659866859</v>
+        <v>-0.05395909955552042</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.121261359466345</v>
+        <v>3.112895014283604</v>
       </c>
       <c r="F1841" t="n">
         <v>1.498653826120122</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.09881062664808066</v>
+        <v>-0.1197264896049325</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.09597201257705</v>
+        <v>3.08760566739431</v>
       </c>
       <c r="F1842" t="n">
         <v>1.498653826120122</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.1123461104247903</v>
+        <v>-0.1332619733816421</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.081185851054122</v>
+        <v>3.072819505871381</v>
       </c>
       <c r="F1843" t="n">
         <v>1.498653826120122</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.1941180108525419</v>
+        <v>-0.2150338738093938</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.038559816838259</v>
+        <v>3.030193471655519</v>
       </c>
       <c r="F1844" t="n">
         <v>1.525689399526259</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.2613271187244196</v>
+        <v>-0.2822429816812714</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.016441490523211</v>
+        <v>3.00807514534047</v>
       </c>
       <c r="F1845" t="n">
         <v>1.525689399526259</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.4688929031160315</v>
+        <v>-0.4898087660728833</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.931239972885806</v>
+        <v>2.922873627703066</v>
       </c>
       <c r="F1846" t="n">
         <v>1.318123615134647</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153011</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.8866469266628685</v>
+        <v>-0.9075627896197203</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.762065254972135</v>
+        <v>2.753698909789394</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9003695915878102</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.108268860220986</v>
+        <v>-1.129184723177838</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.673282698147809</v>
+        <v>2.664916352965069</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8628434579004411</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.316272918574063</v>
+        <v>-1.337188781530915</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.594973219360504</v>
+        <v>2.586606874177763</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8628434579004411</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.527685339462038</v>
+        <v>-1.54860120241889</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.505489707343302</v>
+        <v>2.497123362160561</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6514310370124661</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.866843717050561</v>
+        <v>-1.887759580007412</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.362910655614342</v>
+        <v>2.354544310431602</v>
       </c>
       <c r="F1851" t="n">
         <v>0.312272659423944</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.19486093877804</v>
+        <v>-2.215776801734892</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.252042056662119</v>
+        <v>2.243675711479378</v>
       </c>
       <c r="F1852" t="n">
         <v>-0.01574456230353516</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.688185810313218</v>
+        <v>-2.70910167327007</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.062810858456616</v>
+        <v>2.054444513273875</v>
       </c>
       <c r="F1853" t="n">
         <v>-0.1207306765431539</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.180570838337315</v>
+        <v>-3.201486701294167</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.866963239290709</v>
+        <v>1.858596894107969</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.6131157045672506</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.565751229267387</v>
+        <v>-3.586667092224239</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.711433621731544</v>
+        <v>1.703067276548803</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.6131157045672506</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.90943400249405</v>
+        <v>-3.930349865450902</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.575729635895495</v>
+        <v>1.567363290712754</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.7210217565944688</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.267084352732399</v>
+        <v>-4.28800021568925</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.428775554456413</v>
+        <v>1.420409209273673</v>
       </c>
       <c r="F1857" t="n">
         <v>-1.078672106832817</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.576318455728449</v>
+        <v>-4.597234318685301</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.306854839958252</v>
+        <v>1.298488494775512</v>
       </c>
       <c r="F1858" t="n">
         <v>-1.078672106832817</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.008124248878237</v>
+        <v>-5.029040111835088</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.120465410165742</v>
+        <v>1.112099064983001</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.215089603274084</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.242818243010789</v>
+        <v>-5.26373410596764</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.014872587514811</v>
+        <v>1.006506242332071</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.208753336044829</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.578480890241241</v>
+        <v>-5.599396753198093</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8791881202785956</v>
+        <v>0.8708217750958553</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.208753336044829</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.942107135141555</v>
+        <v>-5.963022998098406</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7402251825527122</v>
+        <v>0.7318588373699715</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.306974972911954</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.307234517780302</v>
+        <v>-6.328150380737153</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5934287445030448</v>
+        <v>0.5850623993203041</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.603285757210967</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.71582329496098</v>
+        <v>-6.736739157917832</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.428754777645532</v>
+        <v>0.4203884324627918</v>
       </c>
       <c r="F1864" t="n">
         <v>-2.011874534391645</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.128805779102074</v>
+        <v>-7.149721642058926</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2587472164605553</v>
+        <v>0.2503808712778146</v>
       </c>
       <c r="F1865" t="n">
         <v>-2.011874534391645</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.545197653389072</v>
+        <v>-7.566113516345923</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.09018451735463362</v>
+        <v>0.08181817217189291</v>
       </c>
       <c r="F1866" t="n">
         <v>-2.011874534391645</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.921874663918916</v>
+        <v>-7.942790526875767</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.05022759618862516</v>
+        <v>-0.05859394137136587</v>
       </c>
       <c r="F1867" t="n">
         <v>-2.011874534391645</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.267749485903725</v>
+        <v>-8.288665348860576</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1924779598368533</v>
+        <v>-0.200844305019594</v>
       </c>
       <c r="F1868" t="n">
         <v>-2.011874534391645</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.429891756366818</v>
+        <v>-8.450807619323669</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2589299479670895</v>
+        <v>-0.2672962931498302</v>
       </c>
       <c r="F1869" t="n">
         <v>-2.011874534391645</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.726553098177016</v>
+        <v>-8.747468961133867</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3738155087619606</v>
+        <v>-0.3821818539447013</v>
       </c>
       <c r="F1870" t="n">
         <v>-2.080617670125524</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.159902206287251</v>
+        <v>-9.180818069244102</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.551181456540458</v>
+        <v>-0.5595478017231983</v>
       </c>
       <c r="F1871" t="n">
         <v>-2.080617670125524</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.542903595029882</v>
+        <v>-9.563819457986733</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7044841133590944</v>
+        <v>-0.7128504585418352</v>
       </c>
       <c r="F1872" t="n">
         <v>-2.080617670125524</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.700302475243003</v>
+        <v>-9.721218338199854</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7648721494729127</v>
+        <v>-0.773238494655653</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.238016550338645</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.059832797747</v>
+        <v>-10.08074866070386</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9033339751764631</v>
+        <v>-0.9117003203592038</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.238016550338645</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.38623282641202</v>
+        <v>-10.40714868936887</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.025977966685291</v>
+        <v>-1.034344311868031</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.564416579003658</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.60538179448621</v>
+        <v>-10.62629765744307</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.110595803293201</v>
+        <v>-1.118962148475941</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.783565547077855</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.6016908695298</v>
+        <v>-10.62260673248666</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.109119433310636</v>
+        <v>-1.117485778493377</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.783565547077855</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.80594904485967</v>
+        <v>-10.82686490781652</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.185309506323939</v>
+        <v>-1.19367585150668</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.911204491691844</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.02398681649085</v>
+        <v>-11.0449026794477</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.268042060491975</v>
+        <v>-1.276408405674716</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.085975259787743</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.9505169848234</v>
+        <v>-10.97143284778025</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.223282426331574</v>
+        <v>-1.231648771514315</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.012505428120295</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.12564140220994</v>
+        <v>-11.14655726516679</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.278776972538674</v>
+        <v>-1.287143317721415</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.187629845506839</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.36009349622443</v>
+        <v>-11.38100935918128</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.379776975046066</v>
+        <v>-1.388143320228807</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.187629845506839</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.64789734076167</v>
+        <v>-11.66881320371852</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.501570703634938</v>
+        <v>-1.509937048817678</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.475433690044077</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.87772178792549</v>
+        <v>-11.89863765088234</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.592384692661912</v>
+        <v>-1.600751037844653</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.638081227114237</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.10975070766175</v>
+        <v>-12.13066657061861</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.682502531927302</v>
+        <v>-1.690868877110043</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.70009392430266</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.05773519369294</v>
+        <v>-12.07865105664979</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.657705990653376</v>
+        <v>-1.666072335836116</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.70009392430266</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.19940703541706</v>
+        <v>-12.22032289837391</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.715849954241766</v>
+        <v>-1.724216299424506</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.70009392430266</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.29831377587634</v>
+        <v>-12.31922963883319</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.740359240260604</v>
+        <v>-1.748725585443344</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.799000664761936</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.09916166863924</v>
+        <v>-12.12007753159609</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.673749531012447</v>
+        <v>-1.682115876195188</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.633678138812123</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.87331651591983</v>
+        <v>-11.89423237887668</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.573832396888474</v>
+        <v>-1.582198742071215</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.591751463224959</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.58704170359713</v>
+        <v>-11.60795756655398</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.458183327403337</v>
+        <v>-1.466549672586078</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.591751463224959</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.63993699164142</v>
+        <v>-11.66085285459827</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.476707668458944</v>
+        <v>-1.485074013641685</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.586796117136513</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.35602826071267</v>
+        <v>-11.37694412366952</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.357410471848808</v>
+        <v>-1.365776817031549</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.586796117136513</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.24060733657458</v>
+        <v>-11.26152319953143</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.320979364587435</v>
+        <v>-1.329345709770175</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.471375192998417</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.97677046937051</v>
+        <v>-10.99768633232736</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.225328099018715</v>
+        <v>-1.233694444201455</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.471375192998417</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.70952866850211</v>
+        <v>-10.73044453145896</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.120265939170729</v>
+        <v>-1.12863228435347</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.471375192998417</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.58622274002389</v>
+        <v>-10.60713860298074</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.071243882752902</v>
+        <v>-1.079610227935643</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.381957521870854</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.56226919904793</v>
+        <v>-10.58318506200478</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.060993960217025</v>
+        <v>-1.069360305399766</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.358003980894897</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.29820926072513</v>
+        <v>-10.31912512368199</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9686303010496591</v>
+        <v>-0.9769966462323998</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.093944042572101</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.591129637220297</v>
+        <v>-9.612045500177148</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6885854853080251</v>
+        <v>-0.6969518304907654</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.093944042572101</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.550945338854106</v>
+        <v>-9.571861201810957</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6721681420737076</v>
+        <v>-0.6805344872564478</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.05375974420591</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.470875543316302</v>
+        <v>-9.491791406273153</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6407734026378287</v>
+        <v>-0.6491397478205694</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.973689948668106</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.237394321086704</v>
+        <v>-9.258310184043555</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5394564849081371</v>
+        <v>-0.5478228300908778</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.740208726438507</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.057685790942831</v>
+        <v>-9.078601653899682</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4704652831635472</v>
+        <v>-0.4788316283462875</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.683037222275811</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.925410317311943</v>
+        <v>-8.946326180268795</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4221876069641652</v>
+        <v>-0.4305539521469055</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.550761748644925</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.73481064263879</v>
+        <v>-8.810507622665328</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3431326764072669</v>
+        <v>-0.3734114684178826</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.414943191041459</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.735050760578933</v>
+        <v>1.702182090337121</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.485810843955209</v>
+        <v>-8.561507823981747</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2306264157101761</v>
+        <v>-0.2609052077207914</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.414943191041459</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.747957101802592</v>
+        <v>1.71508843156078</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.591400833728313</v>
+        <v>-8.667097813754852</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4008383412186363</v>
+        <v>-0.431117133229252</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.520533180814564</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.556627178339511</v>
+        <v>1.523758508097698</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.61013573584691</v>
+        <v>-8.685832715873449</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3597879601889886</v>
+        <v>-0.3900667521996044</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.520533180814564</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.605171520216597</v>
+        <v>1.572302849974785</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.462195694439311</v>
+        <v>-8.53789267446585</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4204908663141165</v>
+        <v>-0.4507696583247323</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.445431147836319</v>
+        <v>-2.500212264906006</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.497485147073564</v>
+        <v>1.464616476831752</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.437967058050338</v>
+        <v>-8.513664038076877</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4195133980120058</v>
+        <v>-0.4497921900226212</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.475983628517034</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.503308342653469</v>
+        <v>1.470439672411657</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.394418651279647</v>
+        <v>-8.470115631306186</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4090546473988224</v>
+        <v>-0.4393334394094381</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.475983628517034</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.496347730558376</v>
+        <v>1.463479060316563</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963415</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.152270257825789</v>
+        <v>-8.227967237852328</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.297732935636136</v>
+        <v>-0.3280117276467518</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.475983628517034</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.510810084939519</v>
+        <v>1.477941414697707</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.089040886057441</v>
+        <v>-8.16473786608398</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.277909066469602</v>
+        <v>-0.3081878584802178</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.475983628517034</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.505342205398714</v>
+        <v>1.472473535156902</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.902553193680435</v>
+        <v>-7.978250173706974</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.205815895508223</v>
+        <v>-0.2360946875188383</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.23471481907034</v>
+        <v>-2.289495936140028</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.614732914835495</v>
+        <v>1.581864244593682</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.881403994776992</v>
+        <v>-7.957100974803531</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1896552377095202</v>
+        <v>-0.219934029720136</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.213565620166897</v>
+        <v>-2.268346737236584</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.635123412414886</v>
+        <v>1.602254742173074</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.637638552793548</v>
+        <v>-7.713335532820087</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.09636835256909171</v>
+        <v>-0.1266471445797075</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.213565620166897</v>
+        <v>-2.268346737236584</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.630904120761937</v>
+        <v>1.598035450520124</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.373610485600288</v>
+        <v>-7.449307465626827</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.01136718822822802</v>
+        <v>-0.01891160378238776</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.011700221350944</v>
+        <v>-2.066481338420631</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.754147673971525</v>
+        <v>1.721279003729712</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.123760091651214</v>
+        <v>-7.199457071677752</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1040494207915601</v>
+        <v>0.07377062878094431</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.011700221350944</v>
+        <v>-2.066481338420631</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.746889748955227</v>
+        <v>1.714021078713414</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.820192602647235</v>
+        <v>-6.895889582673774</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2290755399138003</v>
+        <v>0.1987967479031845</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.011700221350944</v>
+        <v>-2.066481338420631</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.750488872475876</v>
+        <v>1.717620202234063</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.746712693795221</v>
+        <v>-6.82240967382176</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2717950095091592</v>
+        <v>0.2415162174985439</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.938220312498929</v>
+        <v>-1.993001429568617</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.807904323841638</v>
+        <v>1.775035653599826</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.521679694126398</v>
+        <v>-6.597376674152937</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3608286869929858</v>
+        <v>0.33054989498237</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.713187312830106</v>
+        <v>-1.767968429899794</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.941944601259229</v>
+        <v>1.909075931017416</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353073</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.307045316489991</v>
+        <v>-6.38274229651653</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4513772391018658</v>
+        <v>0.42109844709125</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.498552935193699</v>
+        <v>-1.553334052263387</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.07542002889539</v>
+        <v>2.042551358653578</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544782</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.040444959515639</v>
+        <v>-6.116141939542178</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5392116406754019</v>
+        <v>0.5089328486647866</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.498552935193699</v>
+        <v>-1.553334052263387</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.056614287679186</v>
+        <v>2.023745617437373</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.800014462710779</v>
+        <v>-5.875711442737318</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6371269160222237</v>
+        <v>0.6068481240116079</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.258122438388839</v>
+        <v>-1.312903555458527</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.202615662386979</v>
+        <v>2.169746992145167</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.557223655061334</v>
+        <v>-5.632920635087872</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7381725529168217</v>
+        <v>0.7078937609062064</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.258122438388839</v>
+        <v>-1.312903555458527</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.206544976221799</v>
+        <v>2.173676305979987</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.441283805436148</v>
+        <v>-5.516980785462687</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7852270766842362</v>
+        <v>0.7549482846736204</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.181300707372715</v>
+        <v>-1.236081824442403</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.253316598748814</v>
+        <v>2.220447928507001</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.198628217012985</v>
+        <v>-5.274325197039524</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8792873832734949</v>
+        <v>0.8490085912628795</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.181300707372715</v>
+        <v>-1.236081824442403</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.250314669968807</v>
+        <v>2.217445999726995</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.978607418975974</v>
+        <v>-5.054304399002513</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9688747394989132</v>
+        <v>0.9385959474882979</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.040080862304735</v>
+        <v>-1.094861979374423</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.33662561402021</v>
+        <v>2.303756943778397</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.779358789071165</v>
+        <v>-4.855055769097704</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.06446837426266</v>
+        <v>1.034189582252045</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.040080862304735</v>
+        <v>-1.094861979374423</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.352519796822033</v>
+        <v>2.31965112658022</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.619843685551795</v>
+        <v>-4.695540665578334</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.12942026011071</v>
+        <v>1.099141468100095</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8805657587853651</v>
+        <v>-0.9353468758550526</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.449374703373957</v>
+        <v>2.416506033132144</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.475171540452058</v>
+        <v>-4.550868520478597</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.197377220712045</v>
+        <v>1.167098428701429</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7358936136856278</v>
+        <v>-0.7906747307553152</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.546266092995239</v>
+        <v>2.513397422753426</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.53504636780975</v>
+        <v>-4.610743347836289</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.159464781170394</v>
+        <v>1.129185989159778</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7957684410433199</v>
+        <v>-0.8505495581130074</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.49637868798205</v>
+        <v>2.463510017740237</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.448246870030742</v>
+        <v>-4.523943850057281</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.216585073604563</v>
+        <v>1.186306281593948</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7957684410433199</v>
+        <v>-0.8505495581130074</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.518779181304616</v>
+        <v>2.485910511062803</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.34855425530173</v>
+        <v>-4.424251235328269</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.25653452086958</v>
+        <v>1.226255728858965</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6960758263143081</v>
+        <v>-0.7508569433839956</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.578667151515435</v>
+        <v>2.545798481273622</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.41692444162574</v>
+        <v>-4.492621421652279</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.240193368814678</v>
+        <v>1.209914576804062</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6868001272780931</v>
+        <v>-0.7415812443477806</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.595239493411866</v>
+        <v>2.562370823170053</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.295508011999264</v>
+        <v>-4.371204992025802</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.27919664929716</v>
+        <v>1.248917857286544</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6868001272780931</v>
+        <v>-0.7415812443477806</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.585676202043757</v>
+        <v>2.552807531801945</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.326501171327969</v>
+        <v>-4.402198151354508</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.091508950606065</v>
+        <v>1.061230158595449</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6868001272780931</v>
+        <v>-0.7415812443477806</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.410385767084144</v>
+        <v>2.377517096842332</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.151026911535499</v>
+        <v>-4.226723891562038</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.16626588651484</v>
+        <v>1.135987094504225</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6868001272780931</v>
+        <v>-0.7415812443477806</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.414952999075932</v>
+        <v>2.382084328834119</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.261963164176748</v>
+        <v>-4.337660144203287</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.121902859345138</v>
+        <v>1.091624067334523</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6868001272780931</v>
+        <v>-0.7415812443477806</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.414964472962729</v>
+        <v>2.382095802720917</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.464989741719982</v>
+        <v>-4.54068672174652</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.043823613547751</v>
+        <v>1.013544821537135</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8898267048213265</v>
+        <v>-0.944607821891014</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.296279911656695</v>
+        <v>2.263411241414882</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734158</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.307064142784689</v>
+        <v>-4.382761122811227</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.117166239554</v>
+        <v>1.086887447543385</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8898267048213265</v>
+        <v>-0.944607821891014</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.306452298088827</v>
+        <v>2.273583627847015</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212294</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.455385396595817</v>
+        <v>-4.531082376622356</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.052784008603409</v>
+        <v>1.022505216592793</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8898267048213265</v>
+        <v>-0.944607821891014</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.301398568662687</v>
+        <v>2.268529898420875</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786042</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.456568481246878</v>
+        <v>-4.532265461273417</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.04408655018751</v>
+        <v>1.013807758176895</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8954697532878381</v>
+        <v>-0.9502508703575255</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.289788515027306</v>
+        <v>2.256919844785493</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.333440774252795</v>
+        <v>-4.409137754279334</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.093889506018245</v>
+        <v>1.063610714007629</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8954697532878381</v>
+        <v>-0.9502508703575255</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.290340388060407</v>
+        <v>2.257471717818595</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.240630292801935</v>
+        <v>-4.316327272828474</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.060286390489954</v>
+        <v>1.030007598479339</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8026592718369787</v>
+        <v>-0.8574403889066662</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.275299368822289</v>
+        <v>2.242430698580476</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.81080229429443</v>
+        <v>3.472964083711378</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.888255231107191</v>
+        <v>2.65555519751435</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.240630292801935</v>
+        <v>-4.316327272828474</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.060286390489954</v>
+        <v>1.030007598479339</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8026592718369787</v>
+        <v>-0.8574403889066662</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.881319028093559</v>
+        <v>2.648618994500718</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240427.xlsx
+++ b/tame_output/ON/bt/strategyON_20240427.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-80.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.3%</t>
+          <t>116.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.9%</t>
+          <t>136.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-687.9%</t>
+          <t>-700.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.3%</t>
+          <t>-57.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>353.6%</t>
+          <t>410.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.2%</t>
+          <t>-606.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-275.6%</t>
+          <t>-280.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.8%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-60.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-273.2%</t>
+          <t>-278.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.6%</t>
+          <t>-36.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-309.7%</t>
+          <t>-310.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1036293896815316</v>
+        <v>-0.01980144256506905</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.19860658816935</v>
+        <v>3.149234255270709</v>
       </c>
       <c r="F1839" t="n">
         <v>1.605635449818444</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.1086669804091182</v>
+        <v>-0.01476385183748252</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.199199064645722</v>
+        <v>3.149826731747082</v>
       </c>
       <c r="F1840" t="n">
         <v>1.661279906084761</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.05395909955552042</v>
+        <v>-0.1773899318021211</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.112895014283604</v>
+        <v>3.063522681384964</v>
       </c>
       <c r="F1841" t="n">
         <v>1.498653826120122</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.1197264896049325</v>
+        <v>-0.2431573218515332</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.08760566739431</v>
+        <v>3.038233334495669</v>
       </c>
       <c r="F1842" t="n">
         <v>1.498653826120122</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.1332619733816421</v>
+        <v>-0.2566928056282428</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.072819505871381</v>
+        <v>3.023447172972741</v>
       </c>
       <c r="F1843" t="n">
         <v>1.498653826120122</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.2150338738093938</v>
+        <v>-0.3384647060559944</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.030193471655519</v>
+        <v>2.980821138756879</v>
       </c>
       <c r="F1844" t="n">
         <v>1.525689399526259</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.2822429816812714</v>
+        <v>-0.4056738139278721</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.00807514534047</v>
+        <v>2.95870281244183</v>
       </c>
       <c r="F1845" t="n">
         <v>1.525689399526259</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.4898087660728833</v>
+        <v>-0.613239598319484</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.922873627703066</v>
+        <v>2.873501294804425</v>
       </c>
       <c r="F1846" t="n">
         <v>1.318123615134647</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153011</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.9075627896197203</v>
+        <v>-1.030993621866321</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.753698909789394</v>
+        <v>2.704326576890754</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9003695915878102</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.129184723177838</v>
+        <v>-1.252615555424438</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.664916352965069</v>
+        <v>2.615544020066428</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8628434579004411</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.337188781530915</v>
+        <v>-1.460619613777516</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.586606874177763</v>
+        <v>2.537234541279123</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8628434579004411</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.54860120241889</v>
+        <v>-1.672032034665491</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.497123362160561</v>
+        <v>2.447751029261921</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6514310370124661</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.887759580007412</v>
+        <v>-2.011190412254013</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.354544310431602</v>
+        <v>2.305171977532961</v>
       </c>
       <c r="F1851" t="n">
         <v>0.312272659423944</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.215776801734892</v>
+        <v>-2.339207633981492</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.243675711479378</v>
+        <v>2.194303378580738</v>
       </c>
       <c r="F1852" t="n">
         <v>-0.01574456230353516</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.70910167327007</v>
+        <v>-2.83253250551667</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.054444513273875</v>
+        <v>2.005072180375235</v>
       </c>
       <c r="F1853" t="n">
         <v>-0.1207306765431539</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.201486701294167</v>
+        <v>-3.324917533540767</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.858596894107969</v>
+        <v>1.809224561209329</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.6131157045672506</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.586667092224239</v>
+        <v>-3.71009792447084</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.703067276548803</v>
+        <v>1.653694943650163</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.6131157045672506</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.930349865450902</v>
+        <v>-4.053780697697502</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.567363290712754</v>
+        <v>1.517990957814114</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.7210217565944688</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.28800021568925</v>
+        <v>-4.41143104793585</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.420409209273673</v>
+        <v>1.371036876375032</v>
       </c>
       <c r="F1857" t="n">
         <v>-1.078672106832817</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.597234318685301</v>
+        <v>-4.720665150931901</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.298488494775512</v>
+        <v>1.249116161876872</v>
       </c>
       <c r="F1858" t="n">
         <v>-1.078672106832817</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.029040111835088</v>
+        <v>-5.152470944081688</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.112099064983001</v>
+        <v>1.062726732084361</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.215089603274084</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.26373410596764</v>
+        <v>-5.387164938214241</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.006506242332071</v>
+        <v>0.957133909433431</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.208753336044829</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.599396753198093</v>
+        <v>-5.722827585444693</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8708217750958553</v>
+        <v>0.8214494421972152</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.208753336044829</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.963022998098406</v>
+        <v>-6.086453830345007</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7318588373699715</v>
+        <v>0.6824865044713313</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.306974972911954</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.328150380737153</v>
+        <v>-6.451581212983753</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5850623993203041</v>
+        <v>0.5356900664216639</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.603285757210967</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.736739157917832</v>
+        <v>-6.860169990164431</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4203884324627918</v>
+        <v>0.3710160995641516</v>
       </c>
       <c r="F1864" t="n">
         <v>-2.011874534391645</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.149721642058926</v>
+        <v>-7.273152474305525</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2503808712778146</v>
+        <v>0.2010085383791749</v>
       </c>
       <c r="F1865" t="n">
         <v>-2.011874534391645</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.566113516345923</v>
+        <v>-7.689544348592523</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.08181817217189291</v>
+        <v>0.03244583927325317</v>
       </c>
       <c r="F1866" t="n">
         <v>-2.011874534391645</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.942790526875767</v>
+        <v>-8.066221359122366</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.05859394137136587</v>
+        <v>-0.1079662742700052</v>
       </c>
       <c r="F1867" t="n">
         <v>-2.011874534391645</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.288665348860576</v>
+        <v>-8.412096181107175</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.200844305019594</v>
+        <v>-0.2502166379182338</v>
       </c>
       <c r="F1868" t="n">
         <v>-2.011874534391645</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.450807619323669</v>
+        <v>-8.574238451570269</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2672962931498302</v>
+        <v>-0.3166686260484699</v>
       </c>
       <c r="F1869" t="n">
         <v>-2.011874534391645</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.747468961133867</v>
+        <v>-8.870899793380467</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3821818539447013</v>
+        <v>-0.431554186843341</v>
       </c>
       <c r="F1870" t="n">
         <v>-2.080617670125524</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.180818069244102</v>
+        <v>-9.304248901490702</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5595478017231983</v>
+        <v>-0.6089201346218385</v>
       </c>
       <c r="F1871" t="n">
         <v>-2.080617670125524</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.563819457986733</v>
+        <v>-9.687250290233333</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7128504585418352</v>
+        <v>-0.7622227914404749</v>
       </c>
       <c r="F1872" t="n">
         <v>-2.080617670125524</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.721218338199854</v>
+        <v>-9.844649170446454</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.773238494655653</v>
+        <v>-0.8226108275542932</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.238016550338645</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.08074866070386</v>
+        <v>-10.20417949295046</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9117003203592038</v>
+        <v>-0.9610726532578431</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.238016550338645</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.40714868936887</v>
+        <v>-10.53057952161547</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.034344311868031</v>
+        <v>-1.083716644766672</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.564416579003658</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.62629765744307</v>
+        <v>-10.74972848968967</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.118962148475941</v>
+        <v>-1.168334481374581</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.783565547077855</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.62260673248666</v>
+        <v>-10.74603756473326</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.117485778493377</v>
+        <v>-1.166858111392017</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.783565547077855</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.82686490781652</v>
+        <v>-10.95029574006312</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.19367585150668</v>
+        <v>-1.24304818440532</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.911204491691844</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.0449026794477</v>
+        <v>-11.1683335116943</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.276408405674716</v>
+        <v>-1.325780738573355</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.085975259787743</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.97143284778025</v>
+        <v>-11.09486368002685</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.231648771514315</v>
+        <v>-1.281021104412955</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.012505428120295</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.14655726516679</v>
+        <v>-11.26998809741339</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.287143317721415</v>
+        <v>-1.336515650620055</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.187629845506839</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.38100935918128</v>
+        <v>-11.50444019142788</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.388143320228807</v>
+        <v>-1.437515653127447</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.187629845506839</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.66881320371852</v>
+        <v>-11.79224403596512</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.509937048817678</v>
+        <v>-1.559309381716318</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.475433690044077</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.89863765088234</v>
+        <v>-12.02206848312894</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.600751037844653</v>
+        <v>-1.650123370743292</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.638081227114237</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.13066657061861</v>
+        <v>-12.25409740286521</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.690868877110043</v>
+        <v>-1.740241210008682</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.70009392430266</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.07865105664979</v>
+        <v>-12.20208188889639</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.666072335836116</v>
+        <v>-1.715444668734756</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.70009392430266</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.22032289837391</v>
+        <v>-12.34375373062051</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.724216299424506</v>
+        <v>-1.773588632323146</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.70009392430266</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.31922963883319</v>
+        <v>-12.44266047107979</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.748725585443344</v>
+        <v>-1.798097918341984</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.799000664761936</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.12007753159609</v>
+        <v>-12.24350836384269</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.682115876195188</v>
+        <v>-1.731488209093828</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.633678138812123</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.89423237887668</v>
+        <v>-12.01766321112328</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.582198742071215</v>
+        <v>-1.631571074969854</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.591751463224959</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.60795756655398</v>
+        <v>-11.73138839880058</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.466549672586078</v>
+        <v>-1.515922005484717</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.591751463224959</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.66085285459827</v>
+        <v>-11.78428368684487</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.485074013641685</v>
+        <v>-1.534446346540324</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.586796117136513</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.37694412366952</v>
+        <v>-11.50037495591612</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.365776817031549</v>
+        <v>-1.415149149930188</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.586796117136513</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.26152319953143</v>
+        <v>-11.38495403177802</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.329345709770175</v>
+        <v>-1.378718042668814</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.471375192998417</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.99768633232736</v>
+        <v>-11.12111716457395</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.233694444201455</v>
+        <v>-1.283066777100094</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.471375192998417</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.73044453145896</v>
+        <v>-10.85387536370556</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.12863228435347</v>
+        <v>-1.178004617252109</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.471375192998417</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.60713860298074</v>
+        <v>-10.73056943522734</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.079610227935643</v>
+        <v>-1.128982560834282</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.381957521870854</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.58318506200478</v>
+        <v>-10.70661589425138</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.069360305399766</v>
+        <v>-1.118732638298405</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.358003980894897</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.31912512368199</v>
+        <v>-10.44255595592858</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9769966462323998</v>
+        <v>-1.026368979131039</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.093944042572101</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.612045500177148</v>
+        <v>-9.735476332423746</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6969518304907654</v>
+        <v>-0.7463241633894047</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.093944042572101</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.571861201810957</v>
+        <v>-9.695292034057555</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6805344872564478</v>
+        <v>-0.7299068201550871</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.05375974420591</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.491791406273153</v>
+        <v>-9.615222238519751</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6491397478205694</v>
+        <v>-0.6985120807192082</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.973689948668106</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.258310184043555</v>
+        <v>-9.381741016290153</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5478228300908778</v>
+        <v>-0.5971951629895171</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.740208726438507</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.078601653899682</v>
+        <v>-9.20203248614628</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4788316283462875</v>
+        <v>-0.5282039612449267</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.683037222275811</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.946326180268795</v>
+        <v>-9.069757012515392</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4305539521469055</v>
+        <v>-0.4799262850455448</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.550761748644925</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.810507622665328</v>
+        <v>-8.945561951004848</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3734114684178826</v>
+        <v>-0.4274331997536902</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.414943191041459</v>
+        <v>-2.42656668713438</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.702182090337121</v>
+        <v>1.695207992681369</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.561507823981747</v>
+        <v>-8.696562152321267</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2609052077207914</v>
+        <v>-0.314926939056599</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.414943191041459</v>
+        <v>-2.42656668713438</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.71508843156078</v>
+        <v>1.708114333905027</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.667097813754852</v>
+        <v>-8.802152142094371</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.431117133229252</v>
+        <v>-0.4851388645650596</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.520533180814564</v>
+        <v>-2.532156676907484</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.523758508097698</v>
+        <v>1.516784410441946</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.685832715873449</v>
+        <v>-8.820887044212968</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3900667521996044</v>
+        <v>-0.444088483535412</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.520533180814564</v>
+        <v>-2.532156676907484</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.572302849974785</v>
+        <v>1.565328752319032</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.53789267446585</v>
+        <v>-8.672947002805369</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4507696583247323</v>
+        <v>-0.5047913896605398</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.500212264906006</v>
+        <v>-2.511835760998927</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.464616476831752</v>
+        <v>1.457642379175999</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.513664038076877</v>
+        <v>-8.648718366416396</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4497921900226212</v>
+        <v>-0.5038139213584292</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.475983628517034</v>
+        <v>-2.487607124609955</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.470439672411657</v>
+        <v>1.463465574755904</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.470115631306186</v>
+        <v>-8.605169959645705</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4393334394094381</v>
+        <v>-0.4933551707452457</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.475983628517034</v>
+        <v>-2.487607124609955</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.463479060316563</v>
+        <v>1.456504962660811</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963415</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.227967237852328</v>
+        <v>-8.363021566191847</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3280117276467518</v>
+        <v>-0.3820334589825594</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.475983628517034</v>
+        <v>-2.487607124609955</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.477941414697707</v>
+        <v>1.470967317041954</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.16473786608398</v>
+        <v>-8.2997921944235</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3081878584802178</v>
+        <v>-0.3622095898160254</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.475983628517034</v>
+        <v>-2.487607124609955</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.472473535156902</v>
+        <v>1.465499437501149</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.978250173706974</v>
+        <v>-8.113304502046493</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2360946875188383</v>
+        <v>-0.2901164188546459</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.289495936140028</v>
+        <v>-2.301119432232948</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.581864244593682</v>
+        <v>1.57489014693793</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.957100974803531</v>
+        <v>-8.092155303143048</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.219934029720136</v>
+        <v>-0.2739557610559427</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.268346737236584</v>
+        <v>-2.279970233329505</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.602254742173074</v>
+        <v>1.595280644517321</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.713335532820087</v>
+        <v>-7.848389861159604</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1266471445797075</v>
+        <v>-0.1806688759155146</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.268346737236584</v>
+        <v>-2.279970233329505</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.598035450520124</v>
+        <v>1.591061352864372</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.449307465626827</v>
+        <v>-7.584361793966345</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.01891160378238776</v>
+        <v>-0.07293333511819444</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.066481338420631</v>
+        <v>-2.078104834513552</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.721279003729712</v>
+        <v>1.71430490607396</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.199457071677752</v>
+        <v>-7.33451140001727</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.07377062878094431</v>
+        <v>0.01974889744513719</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.066481338420631</v>
+        <v>-2.078104834513552</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.714021078713414</v>
+        <v>1.707046981057662</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.895889582673774</v>
+        <v>-7.030943911013291</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1987967479031845</v>
+        <v>0.1447750165673778</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.066481338420631</v>
+        <v>-2.078104834513552</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.717620202234063</v>
+        <v>1.710646104578311</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.82240967382176</v>
+        <v>-6.957464002161277</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2415162174985439</v>
+        <v>0.1874944861627368</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.993001429568617</v>
+        <v>-2.004624925661537</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.775035653599826</v>
+        <v>1.768061555944073</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.597376674152937</v>
+        <v>-6.732431002492454</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.33054989498237</v>
+        <v>0.2765281636465629</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.767968429899794</v>
+        <v>-1.779591925992714</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.909075931017416</v>
+        <v>1.902101833361664</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.38274229651653</v>
+        <v>-6.517796624856047</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.42109844709125</v>
+        <v>0.3670767157554429</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.553334052263387</v>
+        <v>-1.564957548356308</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.042551358653578</v>
+        <v>2.035577260997825</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.116141939542178</v>
+        <v>-6.251196267881696</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5089328486647866</v>
+        <v>0.4549111173289795</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.553334052263387</v>
+        <v>-1.564957548356308</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.023745617437373</v>
+        <v>2.016771519781621</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.875711442737318</v>
+        <v>-6.010765771076835</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6068481240116079</v>
+        <v>0.5528263926758008</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.312903555458527</v>
+        <v>-1.324527051551447</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.169746992145167</v>
+        <v>2.162772894489414</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.632920635087872</v>
+        <v>-5.76797496342739</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7078937609062064</v>
+        <v>0.6538720295703992</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.312903555458527</v>
+        <v>-1.324527051551447</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.173676305979987</v>
+        <v>2.166702208324235</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.516980785462687</v>
+        <v>-5.652035113802205</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7549482846736204</v>
+        <v>0.7009265533378133</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.236081824442403</v>
+        <v>-1.247705320535323</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.220447928507001</v>
+        <v>2.213473830851249</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.274325197039524</v>
+        <v>-5.409379525379041</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8490085912628795</v>
+        <v>0.7949868599270724</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.236081824442403</v>
+        <v>-1.247705320535323</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.217445999726995</v>
+        <v>2.210471902071242</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.054304399002513</v>
+        <v>-5.189358727342031</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9385959474882979</v>
+        <v>0.8845742161524908</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.094861979374423</v>
+        <v>-1.106485475467343</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.303756943778397</v>
+        <v>2.296782846122645</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009946</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.855055769097704</v>
+        <v>-4.990110097437221</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.034189582252045</v>
+        <v>0.9801678509162377</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.094861979374423</v>
+        <v>-1.106485475467343</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.31965112658022</v>
+        <v>2.312677028924468</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.695540665578334</v>
+        <v>-4.830594993917852</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.099141468100095</v>
+        <v>1.045119736764287</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9353468758550526</v>
+        <v>-0.9469703719479733</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.416506033132144</v>
+        <v>2.409531935476392</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.550868520478597</v>
+        <v>-4.685922848818114</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.167098428701429</v>
+        <v>1.113076697365622</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7906747307553152</v>
+        <v>-0.8022982268482359</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.513397422753426</v>
+        <v>2.506423325097674</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.610743347836289</v>
+        <v>-4.745797676175807</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.129185989159778</v>
+        <v>1.075164257823971</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.8505495581130074</v>
+        <v>-0.862173054205928</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.463510017740237</v>
+        <v>2.456535920084485</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.523943850057281</v>
+        <v>-4.658998178396798</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.186306281593948</v>
+        <v>1.132284550258141</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.8505495581130074</v>
+        <v>-0.862173054205928</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.485910511062803</v>
+        <v>2.478936413407051</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.424251235328269</v>
+        <v>-4.559305563667786</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.226255728858965</v>
+        <v>1.172233997523157</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.7508569433839956</v>
+        <v>-0.7624804394769162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.545798481273622</v>
+        <v>2.53882438361787</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.492621421652279</v>
+        <v>-4.627675749991797</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.209914576804062</v>
+        <v>1.155892845468256</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7415812443477806</v>
+        <v>-0.7532047404407013</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.562370823170053</v>
+        <v>2.555396725514301</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.371204992025802</v>
+        <v>-4.50625932036532</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.248917857286544</v>
+        <v>1.194896125950737</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7415812443477806</v>
+        <v>-0.7532047404407013</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.552807531801945</v>
+        <v>2.545833434146192</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.402198151354508</v>
+        <v>-4.537252479694025</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.061230158595449</v>
+        <v>1.007208427259642</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7415812443477806</v>
+        <v>-0.7532047404407013</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.377517096842332</v>
+        <v>2.370542999186579</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.226723891562038</v>
+        <v>-4.361778219901556</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.135987094504225</v>
+        <v>1.081965363168418</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7415812443477806</v>
+        <v>-0.7532047404407013</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.382084328834119</v>
+        <v>2.375110231178367</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.337660144203287</v>
+        <v>-4.472714472542805</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.091624067334523</v>
+        <v>1.037602335998716</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7415812443477806</v>
+        <v>-0.7532047404407013</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.382095802720917</v>
+        <v>2.375121705065165</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.54068672174652</v>
+        <v>-4.675741050086038</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.013544821537135</v>
+        <v>0.9595230902013279</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.944607821891014</v>
+        <v>-0.9562313179839347</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.263411241414882</v>
+        <v>2.25643714375913</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734158</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.382761122811227</v>
+        <v>-4.517815451150745</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.086887447543385</v>
+        <v>1.032865716207577</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.944607821891014</v>
+        <v>-0.9562313179839347</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.273583627847015</v>
+        <v>2.266609530191262</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212294</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.531082376622356</v>
+        <v>-4.666136704961874</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.022505216592793</v>
+        <v>0.9684834852569864</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.944607821891014</v>
+        <v>-0.9562313179839347</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.268529898420875</v>
+        <v>2.261555800765123</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202392378604</v>
+        <v>3.752023923786042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.532265461273417</v>
+        <v>-4.667319789612934</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.013807758176895</v>
+        <v>0.9597860268410876</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9502508703575255</v>
+        <v>-0.9618743664504462</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.256919844785493</v>
+        <v>2.249945747129741</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273185</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.409137754279334</v>
+        <v>-4.544192082618851</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.063610714007629</v>
+        <v>1.009588982671823</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9502508703575255</v>
+        <v>-0.9618743664504462</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.257471717818595</v>
+        <v>2.250497620162843</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.316327272828474</v>
+        <v>-4.451381601167991</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.030007598479339</v>
+        <v>0.975985867143532</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8574403889066662</v>
+        <v>-0.8690638849995869</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.242430698580476</v>
+        <v>2.235456600924724</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,19 +46326,19 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.472964083711378</v>
+        <v>3.472964083711379</v>
       </c>
       <c r="C1947" t="n">
         <v>2.65555519751435</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.316327272828474</v>
+        <v>-4.451381601167991</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.030007598479339</v>
+        <v>0.975985867143532</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8574403889066662</v>
+        <v>-0.8690638849995869</v>
       </c>
       <c r="G1947" t="n">
         <v>2.648618994500718</v>

--- a/tame_output/ON/bt/strategyON_20240427.xlsx
+++ b/tame_output/ON/bt/strategyON_20240427.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-46.1%</t>
+          <t>-35.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.4%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.5%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>410.4%</t>
+          <t>410.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.7%</t>
+          <t>-601.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-60.2%</t>
+          <t>-60.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-278.6%</t>
+          <t>-276.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.7%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-310.9%</t>
+          <t>-305.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-181.2%</t>
+          <t>-219.2%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -46329,19 +46329,19 @@
         <v>3.472964083711379</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.65555519751435</v>
+        <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.451381601167991</v>
+        <v>-4.400257485236033</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.975985867143532</v>
+        <v>0.9983089894409161</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8690638849995869</v>
+        <v>-0.8179397690676286</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.648618994500718</v>
+        <v>2.2680045464085</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240427.xlsx
+++ b/tame_output/ON/bt/strategyON_20240427.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.6%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>135.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-57.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>410.5%</t>
+          <t>413.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.6%</t>
+          <t>-600.4%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-44.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-60.4%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.4%</t>
+          <t>-275.9%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-168.0%</t>
+          <t>-166.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-305.8%</t>
+          <t>-304.6%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-219.2%</t>
+          <t>-218.5%</t>
         </is>
       </c>
     </row>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153011</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.79224403596512</v>
+        <v>-11.62530751937059</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.559309381716318</v>
+        <v>-1.492534775078507</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.475433690044077</v>
+        <v>-3.308497173449549</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.072684442957031</v>
+        <v>1.172846352913748</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.02206848312894</v>
+        <v>-11.85513196653442</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.650123370743292</v>
+        <v>-1.58334876410548</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.638081227114237</v>
+        <v>-3.471144710519709</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9762117105534909</v>
+        <v>1.076373620510208</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.25409740286521</v>
+        <v>-12.08716088627068</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.740241210008682</v>
+        <v>-1.67346660337087</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.533157407708132</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9416978208695514</v>
+        <v>1.041859730826268</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.20208188889639</v>
+        <v>-12.03514537230186</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.715444668734756</v>
+        <v>-1.648670062096945</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.533157407708132</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9456881565559523</v>
+        <v>1.045850066512669</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.34375373062051</v>
+        <v>-12.17681721402598</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.773588632323146</v>
+        <v>-1.706814025685334</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.533157407708132</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9442129296572106</v>
+        <v>1.044374839613928</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.44266047107979</v>
+        <v>-12.27572395448526</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.798097918341984</v>
+        <v>-1.731323311704173</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.799000664761936</v>
+        <v>-3.632064148167407</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8999222955465176</v>
+        <v>1.000084205503235</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.24350836384269</v>
+        <v>-12.07657184724816</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.731488209093828</v>
+        <v>-1.664713602456016</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.633678138812123</v>
+        <v>-3.466741622217594</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9860646774697228</v>
+        <v>1.08622658742644</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.01766321112328</v>
+        <v>-11.85072669452875</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.631571074969854</v>
+        <v>-1.564796468332042</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.424814946630431</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.02079975585823</v>
+        <v>1.120961665814947</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.73138839880058</v>
+        <v>-11.56445188220605</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.515922005484717</v>
+        <v>-1.449147398846905</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.424814946630431</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.021938900414288</v>
+        <v>1.122100810371006</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78428368684487</v>
+        <v>-11.61734717025034</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.534446346540324</v>
+        <v>-1.467671739902513</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.419859600541984</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.027545882229464</v>
+        <v>1.127707792186181</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50037495591612</v>
+        <v>-11.33343843932159</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.415149149930188</v>
+        <v>-1.348374543292376</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.419859600541984</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.0332795864681</v>
+        <v>1.133441496424818</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.38495403177802</v>
+        <v>-11.2180175151835</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.378718042668814</v>
+        <v>-1.311943436031003</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.304438676403889</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.092794878557092</v>
+        <v>1.19295678851381</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.12111716457395</v>
+        <v>-10.95418064797943</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.283066777100094</v>
+        <v>-1.216292170462283</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.304438676403889</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.082911397244185</v>
+        <v>1.183073307200902</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.85387536370556</v>
+        <v>-10.68693884711103</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.178004617252109</v>
+        <v>-1.111230010614297</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.304438676403889</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.081076836744811</v>
+        <v>1.181238746701528</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.73056943522734</v>
+        <v>-10.56363291863281</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.128982560834282</v>
+        <v>-1.062207954196471</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.381957521870854</v>
+        <v>-3.215021005276326</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.134427124447888</v>
+        <v>1.234589034404605</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.70661589425138</v>
+        <v>-10.53967937765685</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.118732638298405</v>
+        <v>-1.051958031660594</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.358003980894897</v>
+        <v>-3.191067464300368</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.149467755178956</v>
+        <v>1.249629665135673</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.44255595592858</v>
+        <v>-10.27561943933405</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.026368979131039</v>
+        <v>-0.9595943724932274</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.093944042572101</v>
+        <v>-2.927007525977572</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.294643402010882</v>
+        <v>1.394805311967599</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.735476332423746</v>
+        <v>-9.568539815829217</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7463241633894047</v>
+        <v>-0.679549556751593</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.093944042572101</v>
+        <v>-2.927007525977572</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.291856368350581</v>
+        <v>1.392018278307298</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.695292034057555</v>
+        <v>-9.528355517463027</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7299068201550871</v>
+        <v>-0.6631322135172755</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.05375974420591</v>
+        <v>-2.886823227611381</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.316310571258137</v>
+        <v>1.416472481214854</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.615222238519751</v>
+        <v>-9.448285721925222</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6985120807192082</v>
+        <v>-0.631737474081397</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.973689948668106</v>
+        <v>-2.806753432073577</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.363719269801576</v>
+        <v>1.463881179758293</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.381741016290153</v>
+        <v>-9.214804499695624</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5971951629895171</v>
+        <v>-0.5304205563517055</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.740208726438507</v>
+        <v>-2.573272209843978</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.511732431977188</v>
+        <v>1.611894341933905</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.20203248614628</v>
+        <v>-9.035095969551751</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5282039612449267</v>
+        <v>-0.4614293546071151</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.683037222275811</v>
+        <v>-2.516100705681283</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.543143124161846</v>
+        <v>1.643305034118563</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.069757012515392</v>
+        <v>-8.902820495920864</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4799262850455448</v>
+        <v>-0.4131516784077331</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.550761748644925</v>
+        <v>-2.383825232050396</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.617875895087405</v>
+        <v>1.718037805044122</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.945561951004848</v>
+        <v>-8.71222082124771</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4274331997536902</v>
+        <v>-0.3340967478508352</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.42656668713438</v>
+        <v>-2.193225557377243</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.695207992681369</v>
+        <v>1.83521267053565</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.696562152321267</v>
+        <v>-8.463221022564129</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.314926939056599</v>
+        <v>-0.221590487153744</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.42656668713438</v>
+        <v>-2.193225557377243</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.708114333905027</v>
+        <v>1.848119011759309</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.802152142094371</v>
+        <v>-8.568811012337234</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4851388645650596</v>
+        <v>-0.3918024126622046</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.532156676907484</v>
+        <v>-2.298815547150348</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.516784410441946</v>
+        <v>1.656789088296228</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.820887044212968</v>
+        <v>-8.587545914455831</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.444088483535412</v>
+        <v>-0.350752031632557</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.532156676907484</v>
+        <v>-2.298815547150348</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.565328752319032</v>
+        <v>1.705333430173314</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.672947002805369</v>
+        <v>-8.439605873048231</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5047913896605398</v>
+        <v>-0.4114549377576848</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.511835760998927</v>
+        <v>-2.27849463124179</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.457642379175999</v>
+        <v>1.597647057030281</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.648718366416396</v>
+        <v>-8.415377236659259</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5038139213584292</v>
+        <v>-0.4104774694555742</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.487607124609955</v>
+        <v>-2.254265994852818</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.463465574755904</v>
+        <v>1.603470252610186</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.605169959645705</v>
+        <v>-8.371828829888567</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4933551707452457</v>
+        <v>-0.4000187188423907</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.487607124609955</v>
+        <v>-2.254265994852818</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.456504962660811</v>
+        <v>1.596509640515093</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963415</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.363021566191847</v>
+        <v>-8.129680436434709</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3820334589825594</v>
+        <v>-0.2886970070797044</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.487607124609955</v>
+        <v>-2.254265994852818</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.470967317041954</v>
+        <v>1.610971994896236</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.2997921944235</v>
+        <v>-8.066451064666362</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3622095898160254</v>
+        <v>-0.2688731379131704</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.487607124609955</v>
+        <v>-2.254265994852818</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.465499437501149</v>
+        <v>1.605504115355431</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.113304502046493</v>
+        <v>-7.879963372289356</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2901164188546459</v>
+        <v>-0.1967799669517909</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.301119432232948</v>
+        <v>-2.067778302475812</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.57489014693793</v>
+        <v>1.714894824792212</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.092155303143048</v>
+        <v>-7.858814173385912</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2739557610559427</v>
+        <v>-0.1806193091530885</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.279970233329505</v>
+        <v>-2.046629103572368</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.595280644517321</v>
+        <v>1.735285322371603</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.848389861159604</v>
+        <v>-7.615048731402468</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1806688759155146</v>
+        <v>-0.08733242401266006</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.279970233329505</v>
+        <v>-2.046629103572368</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.591061352864372</v>
+        <v>1.731066030718654</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.584361793966345</v>
+        <v>-7.351020664209209</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.07293333511819444</v>
+        <v>0.02040311678465967</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.078104834513552</v>
+        <v>-1.844763704756415</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.71430490607396</v>
+        <v>1.854309583928242</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.33451140001727</v>
+        <v>-7.101170270260134</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.01974889744513719</v>
+        <v>0.1130853493479917</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.078104834513552</v>
+        <v>-1.844763704756415</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.707046981057662</v>
+        <v>1.847051658911944</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.030943911013291</v>
+        <v>-6.797602781256155</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1447750165673778</v>
+        <v>0.2381114684702319</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.078104834513552</v>
+        <v>-1.844763704756415</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.710646104578311</v>
+        <v>1.850650782432593</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.957464002161277</v>
+        <v>-6.724122872404141</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1874944861627368</v>
+        <v>0.2808309380655913</v>
       </c>
       <c r="F1921" t="n">
-        <v>-2.004624925661537</v>
+        <v>-1.7712837959044</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.768061555944073</v>
+        <v>1.908066233798355</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.732431002492454</v>
+        <v>-6.499089872735318</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2765281636465629</v>
+        <v>0.3698646155494174</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.779591925992714</v>
+        <v>-1.546250796235578</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.902101833361664</v>
+        <v>2.042106511215946</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353073</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.517796624856047</v>
+        <v>-6.284455495098912</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3670767157554429</v>
+        <v>0.4604131676582974</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.564957548356308</v>
+        <v>-1.331616418599171</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.035577260997825</v>
+        <v>2.175581938852107</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544782</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.251196267881696</v>
+        <v>-6.01785513812456</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4549111173289795</v>
+        <v>0.5482475692318336</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.564957548356308</v>
+        <v>-1.331616418599171</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.016771519781621</v>
+        <v>2.156776197635903</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.010765771076835</v>
+        <v>-5.777424641319699</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5528263926758008</v>
+        <v>0.6461628445786554</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.324527051551447</v>
+        <v>-1.091185921794311</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.162772894489414</v>
+        <v>2.302777572343696</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.76797496342739</v>
+        <v>-5.534633833670254</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6538720295703992</v>
+        <v>0.7472084814732538</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.324527051551447</v>
+        <v>-1.091185921794311</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.166702208324235</v>
+        <v>2.306706886178516</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.652035113802205</v>
+        <v>-5.418693984045069</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7009265533378133</v>
+        <v>0.7942630052406678</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.247705320535323</v>
+        <v>-1.014364190778187</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.213473830851249</v>
+        <v>2.353478508705531</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.409379525379041</v>
+        <v>-5.176038395621905</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7949868599270724</v>
+        <v>0.888323311829927</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.247705320535323</v>
+        <v>-1.014364190778187</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.210471902071242</v>
+        <v>2.350476579925525</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.189358727342031</v>
+        <v>-4.956017597584895</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8845742161524908</v>
+        <v>0.9779106680553451</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.106485475467343</v>
+        <v>-0.8731443457102064</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.296782846122645</v>
+        <v>2.436787523976927</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.990110097437221</v>
+        <v>-4.756768967680086</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9801678509162377</v>
+        <v>1.073504302819092</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.106485475467343</v>
+        <v>-0.8731443457102064</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.312677028924468</v>
+        <v>2.45268170677875</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.830594993917852</v>
+        <v>-4.597253864160716</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.045119736764287</v>
+        <v>1.138456188667142</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9469703719479733</v>
+        <v>-0.7136292421908365</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.409531935476392</v>
+        <v>2.549536613330674</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.685922848818114</v>
+        <v>-4.452581719060978</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.113076697365622</v>
+        <v>1.206413149268477</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.8022982268482359</v>
+        <v>-0.5689570970910991</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.506423325097674</v>
+        <v>2.646428002951956</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.745797676175807</v>
+        <v>-4.512456546418671</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.075164257823971</v>
+        <v>1.168500709726826</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.862173054205928</v>
+        <v>-0.6288319244487912</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.456535920084485</v>
+        <v>2.596540597938767</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.658998178396798</v>
+        <v>-4.425657048639662</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.132284550258141</v>
+        <v>1.225621002160995</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.862173054205928</v>
+        <v>-0.6288319244487912</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.478936413407051</v>
+        <v>2.618941091261333</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.559305563667786</v>
+        <v>-4.32596443391065</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.172233997523157</v>
+        <v>1.265570449426012</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.7624804394769162</v>
+        <v>-0.5291393097197794</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.53882438361787</v>
+        <v>2.678829061472152</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.627675749991797</v>
+        <v>-4.394334620234661</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.155892845468256</v>
+        <v>1.24922929737111</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7532047404407013</v>
+        <v>-0.5198636106835645</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.555396725514301</v>
+        <v>2.695401403368583</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.50625932036532</v>
+        <v>-4.272918190608184</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.194896125950737</v>
+        <v>1.288232577853592</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7532047404407013</v>
+        <v>-0.5198636106835645</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.545833434146192</v>
+        <v>2.685838112000474</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.537252479694025</v>
+        <v>-4.30391134993689</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.007208427259642</v>
+        <v>1.100544879162496</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7532047404407013</v>
+        <v>-0.5198636106835645</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.370542999186579</v>
+        <v>2.510547677040861</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.361778219901556</v>
+        <v>-4.12843709014442</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.081965363168418</v>
+        <v>1.175301815071272</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7532047404407013</v>
+        <v>-0.5198636106835645</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.375110231178367</v>
+        <v>2.515114909032649</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.472714472542805</v>
+        <v>-4.239373342785669</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.037602335998716</v>
+        <v>1.13093878790157</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7532047404407013</v>
+        <v>-0.5198636106835645</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.375121705065165</v>
+        <v>2.515126382919446</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.675741050086038</v>
+        <v>-4.442399920328902</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9595230902013279</v>
+        <v>1.052859542104182</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.9562313179839347</v>
+        <v>-0.7228901882267978</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.25643714375913</v>
+        <v>2.396441821613412</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734158</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.517815451150745</v>
+        <v>-4.284474321393609</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.032865716207577</v>
+        <v>1.126202168110432</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.9562313179839347</v>
+        <v>-0.7228901882267978</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.266609530191262</v>
+        <v>2.406614208045544</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212294</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.666136704961874</v>
+        <v>-4.432795575204738</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9684834852569864</v>
+        <v>1.061819937159841</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.9562313179839347</v>
+        <v>-0.7228901882267978</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.261555800765123</v>
+        <v>2.401560478619404</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786042</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.667319789612934</v>
+        <v>-4.433978659855798</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9597860268410876</v>
+        <v>1.053122478743942</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9618743664504462</v>
+        <v>-0.7285332366933094</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.249945747129741</v>
+        <v>2.389950424984023</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.544192082618851</v>
+        <v>-4.310850952861715</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.009588982671823</v>
+        <v>1.102925434574677</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9618743664504462</v>
+        <v>-0.7285332366933094</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.250497620162843</v>
+        <v>2.390502298017125</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279494</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.451381601167991</v>
+        <v>-4.218040471410855</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.975985867143532</v>
+        <v>1.069322319046386</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8690638849995869</v>
+        <v>-0.63572275524245</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.235456600924724</v>
+        <v>2.375461278779006</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.472964083711379</v>
+        <v>3.841151522283393</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.400257485236033</v>
+        <v>-4.387963753735952</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9983089894409161</v>
+        <v>1.003226482040949</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8179397690676286</v>
+        <v>-0.8056460375675465</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.2680045464085</v>
+        <v>2.275380785308549</v>
       </c>
     </row>
   </sheetData>
